--- a/research/traditional_assets/database/data/poland/poland_auto_parts.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_auto_parts.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1108256153122142</v>
+        <v>0.110651496643121</v>
       </c>
       <c r="C2">
-        <v>66.09999999999999</v>
+        <v>65.5518001432155</v>
       </c>
       <c r="D2">
-        <v>64.28999999999999</v>
+        <v>64.4028001432155</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="G2">
         <v>1.81</v>
@@ -1451,28 +1451,28 @@
         <v>9.01</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03324829999999999</v>
       </c>
       <c r="N2">
-        <v>9.01</v>
+        <v>8.976751699999999</v>
       </c>
       <c r="O2">
-        <v>1.7119</v>
+        <v>1.705582823</v>
       </c>
       <c r="P2">
-        <v>7.2981</v>
+        <v>7.271168876999999</v>
       </c>
       <c r="Q2">
-        <v>10.0881</v>
+        <v>10.061168877</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1108256153122142</v>
+        <v>0.1113576430738596</v>
       </c>
       <c r="T2">
-        <v>1.190966980496056</v>
+        <v>1.200711255791024</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>270.9912988032471</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.110651496643121</v>
+        <v>0.1104773779740278</v>
       </c>
       <c r="C3">
-        <v>65.5518001432155</v>
+        <v>65.00399680956809</v>
       </c>
       <c r="D3">
-        <v>64.4028001432155</v>
+        <v>64.51599680956809</v>
       </c>
       <c r="E3">
-        <v>0.6609999999999999</v>
+        <v>1.322</v>
       </c>
       <c r="F3">
-        <v>0.6609999999999999</v>
+        <v>1.322</v>
       </c>
       <c r="G3">
         <v>1.81</v>
@@ -1533,28 +1533,28 @@
         <v>9.01</v>
       </c>
       <c r="M3">
-        <v>0.03324829999999999</v>
+        <v>0.06649659999999999</v>
       </c>
       <c r="N3">
-        <v>8.976751699999999</v>
+        <v>8.943503399999999</v>
       </c>
       <c r="O3">
-        <v>1.705582823</v>
+        <v>1.699265646</v>
       </c>
       <c r="P3">
-        <v>7.271168876999999</v>
+        <v>7.244237753999999</v>
       </c>
       <c r="Q3">
-        <v>10.061168877</v>
+        <v>10.034237754</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1113576430738596</v>
+        <v>0.1119005285449263</v>
       </c>
       <c r="T3">
-        <v>1.200711255791024</v>
+        <v>1.210654393847113</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>270.9912988032471</v>
+        <v>135.4956494016236</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1104773779740278</v>
+        <v>0.1103032593049346</v>
       </c>
       <c r="C4">
-        <v>65.00399680956809</v>
+        <v>64.45659209356899</v>
       </c>
       <c r="D4">
-        <v>64.51599680956809</v>
+        <v>64.62959209356899</v>
       </c>
       <c r="E4">
-        <v>1.322</v>
+        <v>1.983</v>
       </c>
       <c r="F4">
-        <v>1.322</v>
+        <v>1.983</v>
       </c>
       <c r="G4">
         <v>1.81</v>
@@ -1615,28 +1615,28 @@
         <v>9.01</v>
       </c>
       <c r="M4">
-        <v>0.06649659999999999</v>
+        <v>0.09974489999999998</v>
       </c>
       <c r="N4">
-        <v>8.943503399999999</v>
+        <v>8.910255100000001</v>
       </c>
       <c r="O4">
-        <v>1.699265646</v>
+        <v>1.692948469</v>
       </c>
       <c r="P4">
-        <v>7.244237753999999</v>
+        <v>7.217306631</v>
       </c>
       <c r="Q4">
-        <v>10.034237754</v>
+        <v>10.007306631</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1119005285449263</v>
+        <v>0.1124546075308604</v>
       </c>
       <c r="T4">
-        <v>1.210654393847113</v>
+        <v>1.220802545058998</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>135.4956494016236</v>
+        <v>90.33043293441571</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1103032593049346</v>
+        <v>0.1101291406358413</v>
       </c>
       <c r="C5">
-        <v>64.45659209356899</v>
+        <v>63.90958810450683</v>
       </c>
       <c r="D5">
-        <v>64.62959209356899</v>
+        <v>64.74358810450683</v>
       </c>
       <c r="E5">
-        <v>1.983</v>
+        <v>2.644</v>
       </c>
       <c r="F5">
-        <v>1.983</v>
+        <v>2.644</v>
       </c>
       <c r="G5">
         <v>1.81</v>
@@ -1697,28 +1697,28 @@
         <v>9.01</v>
       </c>
       <c r="M5">
-        <v>0.09974489999999998</v>
+        <v>0.1329932</v>
       </c>
       <c r="N5">
-        <v>8.910255100000001</v>
+        <v>8.8770068</v>
       </c>
       <c r="O5">
-        <v>1.692948469</v>
+        <v>1.686631292</v>
       </c>
       <c r="P5">
-        <v>7.217306631</v>
+        <v>7.190375508000001</v>
       </c>
       <c r="Q5">
-        <v>10.007306631</v>
+        <v>9.980375508000002</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1124546075308604</v>
+        <v>0.1130202298290014</v>
       </c>
       <c r="T5">
-        <v>1.220802545058998</v>
+        <v>1.231162116087798</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>90.33043293441571</v>
+        <v>67.74782470081178</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1101291406358413</v>
+        <v>0.1099550219667481</v>
       </c>
       <c r="C6">
-        <v>63.90958810450683</v>
+        <v>63.36298696657828</v>
       </c>
       <c r="D6">
-        <v>64.74358810450683</v>
+        <v>64.85798696657828</v>
       </c>
       <c r="E6">
-        <v>2.644</v>
+        <v>3.305</v>
       </c>
       <c r="F6">
-        <v>2.644</v>
+        <v>3.305</v>
       </c>
       <c r="G6">
         <v>1.81</v>
@@ -1779,28 +1779,28 @@
         <v>9.01</v>
       </c>
       <c r="M6">
-        <v>0.1329932</v>
+        <v>0.1662415</v>
       </c>
       <c r="N6">
-        <v>8.8770068</v>
+        <v>8.8437585</v>
       </c>
       <c r="O6">
-        <v>1.686631292</v>
+        <v>1.680314115</v>
       </c>
       <c r="P6">
-        <v>7.190375508000001</v>
+        <v>7.163444385</v>
       </c>
       <c r="Q6">
-        <v>9.980375508000002</v>
+        <v>9.953444385000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1130202298290014</v>
+        <v>0.113597759964998</v>
       </c>
       <c r="T6">
-        <v>1.231162116087798</v>
+        <v>1.241739783348782</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>67.74782470081178</v>
+        <v>54.19825976064942</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1099550219667481</v>
+        <v>0.1097809032976549</v>
       </c>
       <c r="C7">
-        <v>63.36298696657828</v>
+        <v>62.81679081902012</v>
       </c>
       <c r="D7">
-        <v>64.85798696657828</v>
+        <v>64.97279081902012</v>
       </c>
       <c r="E7">
-        <v>3.305</v>
+        <v>3.966</v>
       </c>
       <c r="F7">
-        <v>3.305</v>
+        <v>3.966</v>
       </c>
       <c r="G7">
         <v>1.81</v>
@@ -1861,28 +1861,28 @@
         <v>9.01</v>
       </c>
       <c r="M7">
-        <v>0.1662415</v>
+        <v>0.1994898</v>
       </c>
       <c r="N7">
-        <v>8.8437585</v>
+        <v>8.8105102</v>
       </c>
       <c r="O7">
-        <v>1.680314115</v>
+        <v>1.673996938</v>
       </c>
       <c r="P7">
-        <v>7.163444385</v>
+        <v>7.136513261999999</v>
       </c>
       <c r="Q7">
-        <v>9.953444385000001</v>
+        <v>9.926513262</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.113597759964998</v>
+        <v>0.1141875779762286</v>
       </c>
       <c r="T7">
-        <v>1.241739783348782</v>
+        <v>1.252542507360001</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.19825976064942</v>
+        <v>45.16521646720785</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1097809032976549</v>
+        <v>0.1096067846285617</v>
       </c>
       <c r="C8">
-        <v>62.81679081902012</v>
+        <v>62.2710018162423</v>
       </c>
       <c r="D8">
-        <v>64.97279081902012</v>
+        <v>65.0880018162423</v>
       </c>
       <c r="E8">
-        <v>3.965999999999999</v>
+        <v>4.626999999999999</v>
       </c>
       <c r="F8">
-        <v>3.965999999999999</v>
+        <v>4.626999999999999</v>
       </c>
       <c r="G8">
         <v>1.81</v>
@@ -1943,28 +1943,28 @@
         <v>9.01</v>
       </c>
       <c r="M8">
-        <v>0.1994898</v>
+        <v>0.2327380999999999</v>
       </c>
       <c r="N8">
-        <v>8.8105102</v>
+        <v>8.777261899999999</v>
       </c>
       <c r="O8">
-        <v>1.673996938</v>
+        <v>1.667679761</v>
       </c>
       <c r="P8">
-        <v>7.136513261999999</v>
+        <v>7.109582139</v>
       </c>
       <c r="Q8">
-        <v>9.926513262</v>
+        <v>9.899582139</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1141875779762286</v>
+        <v>0.1147900802457653</v>
       </c>
       <c r="T8">
-        <v>1.252542507360001</v>
+        <v>1.263577548016622</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.16521646720786</v>
+        <v>38.71304268617816</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1096067846285617</v>
+        <v>0.1094326659594685</v>
       </c>
       <c r="C9">
-        <v>62.2710018162423</v>
+        <v>61.72562212796306</v>
       </c>
       <c r="D9">
-        <v>65.0880018162423</v>
+        <v>65.20362212796306</v>
       </c>
       <c r="E9">
-        <v>4.627</v>
+        <v>5.287999999999999</v>
       </c>
       <c r="F9">
-        <v>4.627</v>
+        <v>5.287999999999999</v>
       </c>
       <c r="G9">
         <v>1.81</v>
@@ -2025,28 +2025,28 @@
         <v>9.01</v>
       </c>
       <c r="M9">
-        <v>0.2327381</v>
+        <v>0.2659864</v>
       </c>
       <c r="N9">
-        <v>8.777261899999999</v>
+        <v>8.744013600000001</v>
       </c>
       <c r="O9">
-        <v>1.667679761</v>
+        <v>1.661362584</v>
       </c>
       <c r="P9">
-        <v>7.109582139</v>
+        <v>7.082651016000001</v>
       </c>
       <c r="Q9">
-        <v>9.899582139</v>
+        <v>9.872651016000002</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1147900802457653</v>
+        <v>0.1154056803907267</v>
       </c>
       <c r="T9">
-        <v>1.263577548016622</v>
+        <v>1.27485248086143</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>38.71304268617816</v>
+        <v>33.8739123504059</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1094326659594685</v>
+        <v>0.1092585472903753</v>
       </c>
       <c r="C10">
-        <v>61.72562212796306</v>
+        <v>61.18065393934482</v>
       </c>
       <c r="D10">
-        <v>65.20362212796306</v>
+        <v>65.31965393934482</v>
       </c>
       <c r="E10">
-        <v>5.287999999999999</v>
+        <v>5.948999999999999</v>
       </c>
       <c r="F10">
-        <v>5.287999999999999</v>
+        <v>5.948999999999999</v>
       </c>
       <c r="G10">
         <v>1.81</v>
@@ -2107,28 +2107,28 @@
         <v>9.01</v>
       </c>
       <c r="M10">
-        <v>0.2659864</v>
+        <v>0.2992346999999999</v>
       </c>
       <c r="N10">
-        <v>8.744013600000001</v>
+        <v>8.7107653</v>
       </c>
       <c r="O10">
-        <v>1.661362584</v>
+        <v>1.655045407</v>
       </c>
       <c r="P10">
-        <v>7.082651016000001</v>
+        <v>7.055719893</v>
       </c>
       <c r="Q10">
-        <v>9.872651016000002</v>
+        <v>9.845719893000002</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1154056803907267</v>
+        <v>0.1160348102092036</v>
       </c>
       <c r="T10">
-        <v>1.27485248086143</v>
+        <v>1.286375214428102</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.8739123504059</v>
+        <v>30.11014431147191</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1092585472903753</v>
+        <v>0.1090844286212821</v>
       </c>
       <c r="C11">
-        <v>61.18065393934482</v>
+        <v>60.63609945113207</v>
       </c>
       <c r="D11">
-        <v>65.31965393934482</v>
+        <v>65.43609945113207</v>
       </c>
       <c r="E11">
-        <v>5.948999999999999</v>
+        <v>6.609999999999999</v>
       </c>
       <c r="F11">
-        <v>5.948999999999999</v>
+        <v>6.609999999999999</v>
       </c>
       <c r="G11">
         <v>1.81</v>
@@ -2189,28 +2189,28 @@
         <v>9.01</v>
       </c>
       <c r="M11">
-        <v>0.2992346999999999</v>
+        <v>0.3324829999999999</v>
       </c>
       <c r="N11">
-        <v>8.7107653</v>
+        <v>8.677517</v>
       </c>
       <c r="O11">
-        <v>1.655045407</v>
+        <v>1.64872823</v>
       </c>
       <c r="P11">
-        <v>7.055719893</v>
+        <v>7.02878877</v>
       </c>
       <c r="Q11">
-        <v>9.845719893000002</v>
+        <v>9.818788770000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1160348102092036</v>
+        <v>0.1166779206903135</v>
       </c>
       <c r="T11">
-        <v>1.286375214428102</v>
+        <v>1.298154008740701</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.11014431147191</v>
+        <v>27.09912988032471</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1090844286212821</v>
+        <v>0.1089103099521889</v>
       </c>
       <c r="C12">
-        <v>60.63609945113207</v>
+        <v>60.09196087979036</v>
       </c>
       <c r="D12">
-        <v>65.43609945113207</v>
+        <v>65.55296087979036</v>
       </c>
       <c r="E12">
-        <v>6.609999999999999</v>
+        <v>7.270999999999999</v>
       </c>
       <c r="F12">
-        <v>6.609999999999999</v>
+        <v>7.270999999999999</v>
       </c>
       <c r="G12">
         <v>1.81</v>
@@ -2271,28 +2271,28 @@
         <v>9.01</v>
       </c>
       <c r="M12">
-        <v>0.332483</v>
+        <v>0.3657312999999999</v>
       </c>
       <c r="N12">
-        <v>8.677517</v>
+        <v>8.6442687</v>
       </c>
       <c r="O12">
-        <v>1.64872823</v>
+        <v>1.642411053</v>
       </c>
       <c r="P12">
-        <v>7.02878877</v>
+        <v>7.001857647</v>
       </c>
       <c r="Q12">
-        <v>9.818788770000001</v>
+        <v>9.791857647</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1166779206903135</v>
+        <v>0.1173354830923471</v>
       </c>
       <c r="T12">
-        <v>1.298154008740701</v>
+        <v>1.310197495060324</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.09912988032471</v>
+        <v>24.63557261847701</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1089103099521889</v>
+        <v>0.1087361912830957</v>
       </c>
       <c r="C13">
-        <v>60.09196087979036</v>
+        <v>59.548240457647</v>
       </c>
       <c r="D13">
-        <v>65.55296087979036</v>
+        <v>65.670240457647</v>
       </c>
       <c r="E13">
-        <v>7.270999999999999</v>
+        <v>7.931999999999999</v>
       </c>
       <c r="F13">
-        <v>7.270999999999999</v>
+        <v>7.931999999999999</v>
       </c>
       <c r="G13">
         <v>1.81</v>
@@ -2353,28 +2353,28 @@
         <v>9.01</v>
       </c>
       <c r="M13">
-        <v>0.3657312999999999</v>
+        <v>0.3989795999999999</v>
       </c>
       <c r="N13">
-        <v>8.6442687</v>
+        <v>8.611020399999999</v>
       </c>
       <c r="O13">
-        <v>1.642411053</v>
+        <v>1.636093876</v>
       </c>
       <c r="P13">
-        <v>7.001857647</v>
+        <v>6.974926523999999</v>
       </c>
       <c r="Q13">
-        <v>9.791857647</v>
+        <v>9.764926524</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1173354830923471</v>
+        <v>0.1180079900944269</v>
       </c>
       <c r="T13">
-        <v>1.310197495060324</v>
+        <v>1.32251469697812</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.63557261847701</v>
+        <v>22.58260823360392</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1087361912830957</v>
+        <v>0.1085620726140025</v>
       </c>
       <c r="C14">
-        <v>59.548240457647</v>
+        <v>59.0049404330332</v>
       </c>
       <c r="D14">
-        <v>65.670240457647</v>
+        <v>65.7879404330332</v>
       </c>
       <c r="E14">
-        <v>7.931999999999999</v>
+        <v>8.593</v>
       </c>
       <c r="F14">
-        <v>7.931999999999999</v>
+        <v>8.593</v>
       </c>
       <c r="G14">
         <v>1.81</v>
@@ -2435,28 +2435,28 @@
         <v>9.01</v>
       </c>
       <c r="M14">
-        <v>0.3989795999999999</v>
+        <v>0.4322279</v>
       </c>
       <c r="N14">
-        <v>8.611020399999999</v>
+        <v>8.577772100000001</v>
       </c>
       <c r="O14">
-        <v>1.636093876</v>
+        <v>1.629776699</v>
       </c>
       <c r="P14">
-        <v>6.974926523999999</v>
+        <v>6.947995401</v>
       </c>
       <c r="Q14">
-        <v>9.764926524</v>
+        <v>9.737995401000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1180079900944269</v>
+        <v>0.1186959570275891</v>
       </c>
       <c r="T14">
-        <v>1.32251469697812</v>
+        <v>1.335115052962992</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.58260823360392</v>
+        <v>20.8454845233267</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1085620726140025</v>
+        <v>0.1083879539449093</v>
       </c>
       <c r="C15">
-        <v>59.0049404330332</v>
+        <v>58.46206307042771</v>
       </c>
       <c r="D15">
-        <v>65.7879404330332</v>
+        <v>65.90606307042771</v>
       </c>
       <c r="E15">
-        <v>8.593</v>
+        <v>9.254</v>
       </c>
       <c r="F15">
-        <v>8.593</v>
+        <v>9.254</v>
       </c>
       <c r="G15">
         <v>1.81</v>
@@ -2517,28 +2517,28 @@
         <v>9.01</v>
       </c>
       <c r="M15">
-        <v>0.4322279</v>
+        <v>0.4654762</v>
       </c>
       <c r="N15">
-        <v>8.577772100000001</v>
+        <v>8.5445238</v>
       </c>
       <c r="O15">
-        <v>1.629776699</v>
+        <v>1.623459522</v>
       </c>
       <c r="P15">
-        <v>6.947995401</v>
+        <v>6.921064278</v>
       </c>
       <c r="Q15">
-        <v>9.737995401000001</v>
+        <v>9.711064278000002</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1186959570275891</v>
+        <v>0.119399923191755</v>
       </c>
       <c r="T15">
-        <v>1.335115052962992</v>
+        <v>1.348008440482396</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.8454845233267</v>
+        <v>19.35652134308908</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1083879539449093</v>
+        <v>0.1082138352758161</v>
       </c>
       <c r="C16">
-        <v>58.46206307042771</v>
+        <v>57.91961065060216</v>
       </c>
       <c r="D16">
-        <v>65.90606307042771</v>
+        <v>66.02461065060216</v>
       </c>
       <c r="E16">
-        <v>9.254</v>
+        <v>9.915000000000001</v>
       </c>
       <c r="F16">
-        <v>9.254</v>
+        <v>9.915000000000001</v>
       </c>
       <c r="G16">
         <v>1.81</v>
@@ -2599,28 +2599,28 @@
         <v>9.01</v>
       </c>
       <c r="M16">
-        <v>0.4654762</v>
+        <v>0.4987245</v>
       </c>
       <c r="N16">
-        <v>8.5445238</v>
+        <v>8.5112755</v>
       </c>
       <c r="O16">
-        <v>1.623459522</v>
+        <v>1.617142345</v>
       </c>
       <c r="P16">
-        <v>6.921064278</v>
+        <v>6.894133155</v>
       </c>
       <c r="Q16">
-        <v>9.711064278000002</v>
+        <v>9.684133155000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.119399923191755</v>
+        <v>0.120120453265666</v>
       </c>
       <c r="T16">
-        <v>1.348008440482396</v>
+        <v>1.361205201825786</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.35652134308908</v>
+        <v>18.06608658688314</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1082138352758161</v>
+        <v>0.1080397166067229</v>
       </c>
       <c r="C17">
-        <v>57.91961065060216</v>
+        <v>57.37758547076769</v>
       </c>
       <c r="D17">
-        <v>66.02461065060216</v>
+        <v>66.14358547076769</v>
       </c>
       <c r="E17">
-        <v>9.914999999999999</v>
+        <v>10.576</v>
       </c>
       <c r="F17">
-        <v>9.914999999999999</v>
+        <v>10.576</v>
       </c>
       <c r="G17">
         <v>1.81</v>
@@ -2681,28 +2681,28 @@
         <v>9.01</v>
       </c>
       <c r="M17">
-        <v>0.4987245</v>
+        <v>0.5319727999999999</v>
       </c>
       <c r="N17">
-        <v>8.5112755</v>
+        <v>8.4780272</v>
       </c>
       <c r="O17">
-        <v>1.617142345</v>
+        <v>1.610825168</v>
       </c>
       <c r="P17">
-        <v>6.894133155</v>
+        <v>6.867202032</v>
       </c>
       <c r="Q17">
-        <v>9.684133155000001</v>
+        <v>9.657202032000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.120120453265666</v>
+        <v>0.1208581388175272</v>
       </c>
       <c r="T17">
-        <v>1.361205201825786</v>
+        <v>1.37471617177259</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.06608658688314</v>
+        <v>16.93695617520294</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1080397166067229</v>
+        <v>0.1078655979376297</v>
       </c>
       <c r="C18">
-        <v>57.37758547076769</v>
+        <v>56.83598984472338</v>
       </c>
       <c r="D18">
-        <v>66.14358547076769</v>
+        <v>66.26298984472338</v>
       </c>
       <c r="E18">
-        <v>10.576</v>
+        <v>11.237</v>
       </c>
       <c r="F18">
-        <v>10.576</v>
+        <v>11.237</v>
       </c>
       <c r="G18">
         <v>1.81</v>
@@ -2763,28 +2763,28 @@
         <v>9.01</v>
       </c>
       <c r="M18">
-        <v>0.5319727999999999</v>
+        <v>0.5652211</v>
       </c>
       <c r="N18">
-        <v>8.4780272</v>
+        <v>8.444778899999999</v>
       </c>
       <c r="O18">
-        <v>1.610825168</v>
+        <v>1.604507991</v>
       </c>
       <c r="P18">
-        <v>6.867202032</v>
+        <v>6.840270908999999</v>
       </c>
       <c r="Q18">
-        <v>9.657202032000001</v>
+        <v>9.630270909</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1208581388175272</v>
+        <v>0.121613599924855</v>
       </c>
       <c r="T18">
-        <v>1.37471617177259</v>
+        <v>1.388552707260281</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.93695617520294</v>
+        <v>15.94066463548512</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1078655979376297</v>
+        <v>0.1076914792685364</v>
       </c>
       <c r="C19">
-        <v>56.83598984472338</v>
+        <v>56.29482610300644</v>
       </c>
       <c r="D19">
-        <v>66.26298984472338</v>
+        <v>66.38282610300644</v>
       </c>
       <c r="E19">
-        <v>11.237</v>
+        <v>11.898</v>
       </c>
       <c r="F19">
-        <v>11.237</v>
+        <v>11.898</v>
       </c>
       <c r="G19">
         <v>1.81</v>
@@ -2845,28 +2845,28 @@
         <v>9.01</v>
       </c>
       <c r="M19">
-        <v>0.5652211</v>
+        <v>0.5984693999999999</v>
       </c>
       <c r="N19">
-        <v>8.444778899999999</v>
+        <v>8.411530599999999</v>
       </c>
       <c r="O19">
-        <v>1.604507991</v>
+        <v>1.598190814</v>
       </c>
       <c r="P19">
-        <v>6.840270908999999</v>
+        <v>6.813339785999999</v>
       </c>
       <c r="Q19">
-        <v>9.630270909</v>
+        <v>9.603339785999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.121613599924855</v>
+        <v>0.1223874869128493</v>
       </c>
       <c r="T19">
-        <v>1.388552707260281</v>
+        <v>1.402726719223281</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.94066463548512</v>
+        <v>15.05507215573595</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1076914792685364</v>
+        <v>0.1075173605994432</v>
       </c>
       <c r="C20">
-        <v>56.29482610300643</v>
+        <v>55.75409659304349</v>
       </c>
       <c r="D20">
-        <v>66.38282610300642</v>
+        <v>66.50309659304348</v>
       </c>
       <c r="E20">
-        <v>11.898</v>
+        <v>12.559</v>
       </c>
       <c r="F20">
-        <v>11.898</v>
+        <v>12.559</v>
       </c>
       <c r="G20">
         <v>1.81</v>
@@ -2927,28 +2927,28 @@
         <v>9.01</v>
       </c>
       <c r="M20">
-        <v>0.5984693999999998</v>
+        <v>0.6317176999999999</v>
       </c>
       <c r="N20">
-        <v>8.411530600000001</v>
+        <v>8.3782823</v>
       </c>
       <c r="O20">
-        <v>1.598190814</v>
+        <v>1.591873637</v>
       </c>
       <c r="P20">
-        <v>6.813339786</v>
+        <v>6.786408663</v>
       </c>
       <c r="Q20">
-        <v>9.603339786000001</v>
+        <v>9.576408663000002</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1223874869128493</v>
+        <v>0.1231804822215349</v>
       </c>
       <c r="T20">
-        <v>1.402726719223281</v>
+        <v>1.417250706790306</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.05507215573595</v>
+        <v>14.26269993701301</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1075173605994432</v>
+        <v>0.1073432419303501</v>
       </c>
       <c r="C21">
-        <v>55.75409659304349</v>
+        <v>55.21380367930412</v>
       </c>
       <c r="D21">
-        <v>66.50309659304348</v>
+        <v>66.62380367930412</v>
       </c>
       <c r="E21">
-        <v>12.559</v>
+        <v>13.22</v>
       </c>
       <c r="F21">
-        <v>12.559</v>
+        <v>13.22</v>
       </c>
       <c r="G21">
         <v>1.81</v>
@@ -3009,28 +3009,28 @@
         <v>9.01</v>
       </c>
       <c r="M21">
-        <v>0.6317176999999999</v>
+        <v>0.6649659999999999</v>
       </c>
       <c r="N21">
-        <v>8.3782823</v>
+        <v>8.345034</v>
       </c>
       <c r="O21">
-        <v>1.591873637</v>
+        <v>1.58555646</v>
       </c>
       <c r="P21">
-        <v>6.786408663</v>
+        <v>6.75947754</v>
       </c>
       <c r="Q21">
-        <v>9.576408663000002</v>
+        <v>9.549477540000002</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1231804822215349</v>
+        <v>0.1239933024129376</v>
       </c>
       <c r="T21">
-        <v>1.417250706790306</v>
+        <v>1.432137794046507</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.26269993701301</v>
+        <v>13.54956494016236</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1073432419303501</v>
+        <v>0.1071691232612569</v>
       </c>
       <c r="C22">
-        <v>55.21380367930412</v>
+        <v>54.67394974345582</v>
       </c>
       <c r="D22">
-        <v>66.62380367930412</v>
+        <v>66.74494974345582</v>
       </c>
       <c r="E22">
-        <v>13.22</v>
+        <v>13.881</v>
       </c>
       <c r="F22">
-        <v>13.22</v>
+        <v>13.881</v>
       </c>
       <c r="G22">
         <v>1.81</v>
@@ -3091,28 +3091,28 @@
         <v>9.01</v>
       </c>
       <c r="M22">
-        <v>0.6649659999999999</v>
+        <v>0.6982143</v>
       </c>
       <c r="N22">
-        <v>8.345034</v>
+        <v>8.3117857</v>
       </c>
       <c r="O22">
-        <v>1.58555646</v>
+        <v>1.579239283</v>
       </c>
       <c r="P22">
-        <v>6.75947754</v>
+        <v>6.732546417</v>
       </c>
       <c r="Q22">
-        <v>9.549477540000002</v>
+        <v>9.522546417000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1239933024129376</v>
+        <v>0.1248267003307049</v>
       </c>
       <c r="T22">
-        <v>1.432137794046507</v>
+        <v>1.447401769587675</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.54956494016236</v>
+        <v>12.90434756205939</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1071691232612569</v>
+        <v>0.1072623045921636</v>
       </c>
       <c r="C23">
-        <v>54.67394974345582</v>
+        <v>53.94806248073419</v>
       </c>
       <c r="D23">
-        <v>66.74494974345582</v>
+        <v>66.68006248073419</v>
       </c>
       <c r="E23">
-        <v>13.881</v>
+        <v>14.542</v>
       </c>
       <c r="F23">
-        <v>13.881</v>
+        <v>14.542</v>
       </c>
       <c r="G23">
         <v>1.81</v>
@@ -3173,45 +3173,45 @@
         <v>9.01</v>
       </c>
       <c r="M23">
-        <v>0.6982142999999998</v>
+        <v>0.7532755999999999</v>
       </c>
       <c r="N23">
-        <v>8.3117857</v>
+        <v>8.2567244</v>
       </c>
       <c r="O23">
-        <v>1.579239283</v>
+        <v>1.568777636</v>
       </c>
       <c r="P23">
-        <v>6.732546417</v>
+        <v>6.687946763999999</v>
       </c>
       <c r="Q23">
-        <v>9.522546417000001</v>
+        <v>9.477946764</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1248267003307049</v>
+        <v>0.1256814674258508</v>
       </c>
       <c r="T23">
-        <v>1.447401769587675</v>
+        <v>1.463057129117078</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.19</v>
       </c>
       <c r="W23">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>12.90434756205939</v>
+        <v>11.96109365549608</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1072623045921636</v>
+        <v>0.1071003359230704</v>
       </c>
       <c r="C24">
-        <v>53.94806248073419</v>
+        <v>53.39993121394076</v>
       </c>
       <c r="D24">
-        <v>66.68006248073419</v>
+        <v>66.79293121394076</v>
       </c>
       <c r="E24">
-        <v>14.542</v>
+        <v>15.203</v>
       </c>
       <c r="F24">
-        <v>14.542</v>
+        <v>15.203</v>
       </c>
       <c r="G24">
         <v>1.81</v>
@@ -3255,28 +3255,28 @@
         <v>9.01</v>
       </c>
       <c r="M24">
-        <v>0.7532755999999999</v>
+        <v>0.7875154</v>
       </c>
       <c r="N24">
-        <v>8.2567244</v>
+        <v>8.2224846</v>
       </c>
       <c r="O24">
-        <v>1.568777636</v>
+        <v>1.562272074</v>
       </c>
       <c r="P24">
-        <v>6.687946763999999</v>
+        <v>6.660212526</v>
       </c>
       <c r="Q24">
-        <v>9.477946764</v>
+        <v>9.450212526000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1256814674258508</v>
+        <v>0.1265584362637278</v>
       </c>
       <c r="T24">
-        <v>1.463057129117078</v>
+        <v>1.47911912136153</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.96109365549608</v>
+        <v>11.44104610525712</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1071003359230704</v>
+        <v>0.1069383672539772</v>
       </c>
       <c r="C25">
-        <v>53.39993121394076</v>
+        <v>52.85218269877672</v>
       </c>
       <c r="D25">
-        <v>66.79293121394076</v>
+        <v>66.90618269877672</v>
       </c>
       <c r="E25">
-        <v>15.203</v>
+        <v>15.864</v>
       </c>
       <c r="F25">
-        <v>15.203</v>
+        <v>15.864</v>
       </c>
       <c r="G25">
         <v>1.81</v>
@@ -3337,28 +3337,28 @@
         <v>9.01</v>
       </c>
       <c r="M25">
-        <v>0.7875154</v>
+        <v>0.8217552</v>
       </c>
       <c r="N25">
-        <v>8.2224846</v>
+        <v>8.1882448</v>
       </c>
       <c r="O25">
-        <v>1.562272074</v>
+        <v>1.555766512</v>
       </c>
       <c r="P25">
-        <v>6.660212526</v>
+        <v>6.632478288</v>
       </c>
       <c r="Q25">
-        <v>9.450212526000001</v>
+        <v>9.422478288000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1265584362637278</v>
+        <v>0.1274584832289174</v>
       </c>
       <c r="T25">
-        <v>1.47911912136153</v>
+        <v>1.495603797612415</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.44104610525712</v>
+        <v>10.9643358508714</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1069383672539772</v>
+        <v>0.106776398584884</v>
       </c>
       <c r="C26">
-        <v>52.85218269877672</v>
+        <v>52.30481888548497</v>
       </c>
       <c r="D26">
-        <v>66.90618269877672</v>
+        <v>67.01981888548497</v>
       </c>
       <c r="E26">
-        <v>15.864</v>
+        <v>16.525</v>
       </c>
       <c r="F26">
-        <v>15.864</v>
+        <v>16.525</v>
       </c>
       <c r="G26">
         <v>1.81</v>
@@ -3419,28 +3419,28 @@
         <v>9.01</v>
       </c>
       <c r="M26">
-        <v>0.8217551999999998</v>
+        <v>0.855995</v>
       </c>
       <c r="N26">
-        <v>8.1882448</v>
+        <v>8.154005</v>
       </c>
       <c r="O26">
-        <v>1.555766512</v>
+        <v>1.54926095</v>
       </c>
       <c r="P26">
-        <v>6.632478288</v>
+        <v>6.60474405</v>
       </c>
       <c r="Q26">
-        <v>9.422478288000001</v>
+        <v>9.39474405</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1274584832289174</v>
+        <v>0.128382531446512</v>
       </c>
       <c r="T26">
-        <v>1.495603797612415</v>
+        <v>1.512528065229991</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.96433585087141</v>
+        <v>10.52576241683655</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.106776398584884</v>
+        <v>0.1066144299157908</v>
       </c>
       <c r="C27">
-        <v>52.30481888548497</v>
+        <v>51.75784173758043</v>
       </c>
       <c r="D27">
-        <v>67.01981888548497</v>
+        <v>67.13384173758043</v>
       </c>
       <c r="E27">
-        <v>16.525</v>
+        <v>17.186</v>
       </c>
       <c r="F27">
-        <v>16.525</v>
+        <v>17.186</v>
       </c>
       <c r="G27">
         <v>1.81</v>
@@ -3501,28 +3501,28 @@
         <v>9.01</v>
       </c>
       <c r="M27">
-        <v>0.855995</v>
+        <v>0.8902348</v>
       </c>
       <c r="N27">
-        <v>8.154005</v>
+        <v>8.1197652</v>
       </c>
       <c r="O27">
-        <v>1.54926095</v>
+        <v>1.542755388</v>
       </c>
       <c r="P27">
-        <v>6.60474405</v>
+        <v>6.577009812</v>
       </c>
       <c r="Q27">
-        <v>9.39474405</v>
+        <v>9.367009812000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.128382531446512</v>
+        <v>0.1293315539402578</v>
       </c>
       <c r="T27">
-        <v>1.512528065229991</v>
+        <v>1.529909745485879</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.52576241683655</v>
+        <v>10.12092540080437</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1066144299157908</v>
+        <v>0.1068242512466976</v>
       </c>
       <c r="C28">
-        <v>51.75784173758043</v>
+        <v>50.9492056076975</v>
       </c>
       <c r="D28">
-        <v>67.13384173758043</v>
+        <v>66.9862056076975</v>
       </c>
       <c r="E28">
-        <v>17.186</v>
+        <v>17.847</v>
       </c>
       <c r="F28">
-        <v>17.186</v>
+        <v>17.847</v>
       </c>
       <c r="G28">
         <v>1.81</v>
@@ -3583,45 +3583,45 @@
         <v>9.01</v>
       </c>
       <c r="M28">
-        <v>0.8902348</v>
+        <v>0.9548145</v>
       </c>
       <c r="N28">
-        <v>8.1197652</v>
+        <v>8.0551855</v>
       </c>
       <c r="O28">
-        <v>1.542755388</v>
+        <v>1.530485245</v>
       </c>
       <c r="P28">
-        <v>6.577009812</v>
+        <v>6.524700255</v>
       </c>
       <c r="Q28">
-        <v>9.367009812000001</v>
+        <v>9.314700255000002</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1293315539402578</v>
+        <v>0.1303065770502707</v>
       </c>
       <c r="T28">
-        <v>1.529909745485879</v>
+        <v>1.547767636159737</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.19</v>
       </c>
       <c r="W28">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>10.12092540080437</v>
+        <v>9.436387905713623</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1068242512466976</v>
+        <v>0.1066760525776044</v>
       </c>
       <c r="C29">
-        <v>50.9492056076975</v>
+        <v>50.39241486366045</v>
       </c>
       <c r="D29">
-        <v>66.9862056076975</v>
+        <v>67.09041486366044</v>
       </c>
       <c r="E29">
-        <v>17.847</v>
+        <v>18.508</v>
       </c>
       <c r="F29">
-        <v>17.847</v>
+        <v>18.508</v>
       </c>
       <c r="G29">
         <v>1.81</v>
@@ -3665,28 +3665,28 @@
         <v>9.01</v>
       </c>
       <c r="M29">
-        <v>0.9548145</v>
+        <v>0.9901779999999999</v>
       </c>
       <c r="N29">
-        <v>8.0551855</v>
+        <v>8.019822</v>
       </c>
       <c r="O29">
-        <v>1.530485245</v>
+        <v>1.52376618</v>
       </c>
       <c r="P29">
-        <v>6.524700255</v>
+        <v>6.49605582</v>
       </c>
       <c r="Q29">
-        <v>9.314700255000002</v>
+        <v>9.286055820000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1303065770502707</v>
+        <v>0.1313086841355616</v>
       </c>
       <c r="T29">
-        <v>1.547767636159737</v>
+        <v>1.566121579352313</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.436387905713623</v>
+        <v>9.099374051938137</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1066760525776044</v>
+        <v>0.1065278539085112</v>
       </c>
       <c r="C30">
-        <v>50.39241486366045</v>
+        <v>49.83594885780767</v>
       </c>
       <c r="D30">
-        <v>67.09041486366044</v>
+        <v>67.19494885780766</v>
       </c>
       <c r="E30">
-        <v>18.508</v>
+        <v>19.169</v>
       </c>
       <c r="F30">
-        <v>18.508</v>
+        <v>19.169</v>
       </c>
       <c r="G30">
         <v>1.81</v>
@@ -3747,28 +3747,28 @@
         <v>9.01</v>
       </c>
       <c r="M30">
-        <v>0.9901779999999999</v>
+        <v>1.0255415</v>
       </c>
       <c r="N30">
-        <v>8.019822</v>
+        <v>7.9844585</v>
       </c>
       <c r="O30">
-        <v>1.52376618</v>
+        <v>1.517047115</v>
       </c>
       <c r="P30">
-        <v>6.49605582</v>
+        <v>6.467411385</v>
       </c>
       <c r="Q30">
-        <v>9.286055820000001</v>
+        <v>9.257411385000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1313086841355616</v>
+        <v>0.1323390195894524</v>
       </c>
       <c r="T30">
-        <v>1.566121579352313</v>
+        <v>1.584992535029188</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.099374051938137</v>
+        <v>8.785602532905786</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1065278539085112</v>
+        <v>0.106379655239418</v>
       </c>
       <c r="C31">
-        <v>49.83594885780768</v>
+        <v>49.27980911043775</v>
       </c>
       <c r="D31">
-        <v>67.19494885780767</v>
+        <v>67.29980911043775</v>
       </c>
       <c r="E31">
-        <v>19.169</v>
+        <v>19.83</v>
       </c>
       <c r="F31">
-        <v>19.169</v>
+        <v>19.83</v>
       </c>
       <c r="G31">
         <v>1.81</v>
@@ -3829,28 +3829,28 @@
         <v>9.01</v>
       </c>
       <c r="M31">
-        <v>1.0255415</v>
+        <v>1.060905</v>
       </c>
       <c r="N31">
-        <v>7.9844585</v>
+        <v>7.949095</v>
       </c>
       <c r="O31">
-        <v>1.517047115</v>
+        <v>1.51032805</v>
       </c>
       <c r="P31">
-        <v>6.467411385</v>
+        <v>6.43876695</v>
       </c>
       <c r="Q31">
-        <v>9.257411385000001</v>
+        <v>9.228766950000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1323390195894524</v>
+        <v>0.1333987931991685</v>
       </c>
       <c r="T31">
-        <v>1.584992535029188</v>
+        <v>1.604402660868258</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.785602532905788</v>
+        <v>8.49274911514226</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.106379655239418</v>
+        <v>0.1062314565703247</v>
       </c>
       <c r="C32">
-        <v>49.27980911043775</v>
+        <v>48.723997151354</v>
       </c>
       <c r="D32">
-        <v>67.29980911043775</v>
+        <v>67.404997151354</v>
       </c>
       <c r="E32">
-        <v>19.83</v>
+        <v>20.491</v>
       </c>
       <c r="F32">
-        <v>19.83</v>
+        <v>20.491</v>
       </c>
       <c r="G32">
         <v>1.81</v>
@@ -3911,28 +3911,28 @@
         <v>9.01</v>
       </c>
       <c r="M32">
-        <v>1.060905</v>
+        <v>1.0962685</v>
       </c>
       <c r="N32">
-        <v>7.949095</v>
+        <v>7.9137315</v>
       </c>
       <c r="O32">
-        <v>1.51032805</v>
+        <v>1.503608985</v>
       </c>
       <c r="P32">
-        <v>6.43876695</v>
+        <v>6.410122514999999</v>
       </c>
       <c r="Q32">
-        <v>9.228766950000001</v>
+        <v>9.200122515</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1333987931991685</v>
+        <v>0.1344892848845286</v>
       </c>
       <c r="T32">
-        <v>1.604402660868258</v>
+        <v>1.62437539905049</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.49274911514226</v>
+        <v>8.218789466266704</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1062314565703247</v>
+        <v>0.1060832579012315</v>
       </c>
       <c r="C33">
-        <v>48.723997151354</v>
+        <v>48.16851451993891</v>
       </c>
       <c r="D33">
-        <v>67.404997151354</v>
+        <v>67.51051451993891</v>
       </c>
       <c r="E33">
-        <v>20.491</v>
+        <v>21.152</v>
       </c>
       <c r="F33">
-        <v>20.491</v>
+        <v>21.152</v>
       </c>
       <c r="G33">
         <v>1.81</v>
@@ -3993,28 +3993,28 @@
         <v>9.01</v>
       </c>
       <c r="M33">
-        <v>1.0962685</v>
+        <v>1.131632</v>
       </c>
       <c r="N33">
-        <v>7.9137315</v>
+        <v>7.878368</v>
       </c>
       <c r="O33">
-        <v>1.503608985</v>
+        <v>1.49688992</v>
       </c>
       <c r="P33">
-        <v>6.410122514999999</v>
+        <v>6.38147808</v>
       </c>
       <c r="Q33">
-        <v>9.200122515</v>
+        <v>9.17147808</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1344892848845286</v>
+        <v>0.1356118498547523</v>
       </c>
       <c r="T33">
-        <v>1.62437539905049</v>
+        <v>1.64493557070867</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.218789466266704</v>
+        <v>7.961952295445871</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1060832579012315</v>
+        <v>0.1059350592321384</v>
       </c>
       <c r="C34">
-        <v>48.16851451993891</v>
+        <v>47.61336276522923</v>
       </c>
       <c r="D34">
-        <v>67.51051451993891</v>
+        <v>67.61636276522923</v>
       </c>
       <c r="E34">
-        <v>21.152</v>
+        <v>21.813</v>
       </c>
       <c r="F34">
-        <v>21.152</v>
+        <v>21.813</v>
       </c>
       <c r="G34">
         <v>1.81</v>
@@ -4075,28 +4075,28 @@
         <v>9.01</v>
       </c>
       <c r="M34">
-        <v>1.131632</v>
+        <v>1.1669955</v>
       </c>
       <c r="N34">
-        <v>7.878368</v>
+        <v>7.8430045</v>
       </c>
       <c r="O34">
-        <v>1.49688992</v>
+        <v>1.490170855</v>
       </c>
       <c r="P34">
-        <v>6.38147808</v>
+        <v>6.352833645</v>
       </c>
       <c r="Q34">
-        <v>9.17147808</v>
+        <v>9.142833645000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1356118498547523</v>
+        <v>0.1367679242270722</v>
       </c>
       <c r="T34">
-        <v>1.64493557070867</v>
+        <v>1.666109478834259</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.961952295445871</v>
+        <v>7.720681013765692</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1059350592321384</v>
+        <v>0.1060071805630451</v>
       </c>
       <c r="C35">
-        <v>47.61336276522923</v>
+        <v>46.90080996815178</v>
       </c>
       <c r="D35">
-        <v>67.61636276522923</v>
+        <v>67.56480996815178</v>
       </c>
       <c r="E35">
-        <v>21.813</v>
+        <v>22.474</v>
       </c>
       <c r="F35">
-        <v>21.813</v>
+        <v>22.474</v>
       </c>
       <c r="G35">
         <v>1.81</v>
@@ -4157,45 +4157,45 @@
         <v>9.01</v>
       </c>
       <c r="M35">
-        <v>1.1669955</v>
+        <v>1.2203382</v>
       </c>
       <c r="N35">
-        <v>7.8430045</v>
+        <v>7.789661799999999</v>
       </c>
       <c r="O35">
-        <v>1.490170855</v>
+        <v>1.480035742</v>
       </c>
       <c r="P35">
-        <v>6.352833645</v>
+        <v>6.309626057999999</v>
       </c>
       <c r="Q35">
-        <v>9.142833645000001</v>
+        <v>9.099626058</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1367679242270722</v>
+        <v>0.137959031156129</v>
       </c>
       <c r="T35">
-        <v>1.666109478834259</v>
+        <v>1.68792502053941</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.19</v>
       </c>
       <c r="W35">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.720681013765692</v>
+        <v>7.383199181997252</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1060071805630451</v>
+        <v>0.1058654618939519</v>
       </c>
       <c r="C36">
-        <v>46.90080996815178</v>
+        <v>46.34118604006436</v>
       </c>
       <c r="D36">
-        <v>67.56480996815178</v>
+        <v>67.66618604006436</v>
       </c>
       <c r="E36">
-        <v>22.474</v>
+        <v>23.135</v>
       </c>
       <c r="F36">
-        <v>22.474</v>
+        <v>23.135</v>
       </c>
       <c r="G36">
         <v>1.81</v>
@@ -4239,28 +4239,28 @@
         <v>9.01</v>
       </c>
       <c r="M36">
-        <v>1.2203382</v>
+        <v>1.2562305</v>
       </c>
       <c r="N36">
-        <v>7.789661799999999</v>
+        <v>7.7537695</v>
       </c>
       <c r="O36">
-        <v>1.480035742</v>
+        <v>1.473216205</v>
       </c>
       <c r="P36">
-        <v>6.309626057999999</v>
+        <v>6.280553295</v>
       </c>
       <c r="Q36">
-        <v>9.099626058</v>
+        <v>9.070553295</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.137959031156129</v>
+        <v>0.1391867875291568</v>
       </c>
       <c r="T36">
-        <v>1.68792502053941</v>
+        <v>1.710411809681643</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.383199181997252</v>
+        <v>7.172250633940188</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1058654618939519</v>
+        <v>0.1057237432248587</v>
       </c>
       <c r="C37">
-        <v>46.34118604006436</v>
+        <v>45.78186678392624</v>
       </c>
       <c r="D37">
-        <v>67.66618604006436</v>
+        <v>67.76786678392624</v>
       </c>
       <c r="E37">
-        <v>23.135</v>
+        <v>23.796</v>
       </c>
       <c r="F37">
-        <v>23.135</v>
+        <v>23.796</v>
       </c>
       <c r="G37">
         <v>1.81</v>
@@ -4321,28 +4321,28 @@
         <v>9.01</v>
       </c>
       <c r="M37">
-        <v>1.2562305</v>
+        <v>1.2921228</v>
       </c>
       <c r="N37">
-        <v>7.7537695</v>
+        <v>7.7178772</v>
       </c>
       <c r="O37">
-        <v>1.473216205</v>
+        <v>1.466396668</v>
       </c>
       <c r="P37">
-        <v>6.280553295</v>
+        <v>6.251480532</v>
       </c>
       <c r="Q37">
-        <v>9.070553295</v>
+        <v>9.041480532000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1391867875291568</v>
+        <v>0.1404529112888418</v>
       </c>
       <c r="T37">
-        <v>1.710411809681643</v>
+        <v>1.733601310984572</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.172250633940188</v>
+        <v>6.973021449664072</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1057237432248587</v>
+        <v>0.1055820245557655</v>
       </c>
       <c r="C38">
-        <v>45.78186678392625</v>
+        <v>45.22285357527942</v>
       </c>
       <c r="D38">
-        <v>67.76786678392624</v>
+        <v>67.86985357527941</v>
       </c>
       <c r="E38">
-        <v>23.796</v>
+        <v>24.457</v>
       </c>
       <c r="F38">
-        <v>23.796</v>
+        <v>24.457</v>
       </c>
       <c r="G38">
         <v>1.81</v>
@@ -4403,28 +4403,28 @@
         <v>9.01</v>
       </c>
       <c r="M38">
-        <v>1.2921228</v>
+        <v>1.3280151</v>
       </c>
       <c r="N38">
-        <v>7.7178772</v>
+        <v>7.6819849</v>
       </c>
       <c r="O38">
-        <v>1.466396668</v>
+        <v>1.459577131</v>
       </c>
       <c r="P38">
-        <v>6.251480532</v>
+        <v>6.222407769</v>
       </c>
       <c r="Q38">
-        <v>9.041480532000001</v>
+        <v>9.012407769000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1404529112888418</v>
+        <v>0.1417592294535961</v>
       </c>
       <c r="T38">
-        <v>1.733601310984571</v>
+        <v>1.757526986932037</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.973021449664073</v>
+        <v>6.784561410483963</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1055820245557655</v>
+        <v>0.1054403058866723</v>
       </c>
       <c r="C39">
-        <v>45.22285357527942</v>
+        <v>44.66414779795871</v>
       </c>
       <c r="D39">
-        <v>67.86985357527941</v>
+        <v>67.9721477979587</v>
       </c>
       <c r="E39">
-        <v>24.457</v>
+        <v>25.118</v>
       </c>
       <c r="F39">
-        <v>24.457</v>
+        <v>25.118</v>
       </c>
       <c r="G39">
         <v>1.81</v>
@@ -4485,28 +4485,28 @@
         <v>9.01</v>
       </c>
       <c r="M39">
-        <v>1.3280151</v>
+        <v>1.3639074</v>
       </c>
       <c r="N39">
-        <v>7.6819849</v>
+        <v>7.646092599999999</v>
       </c>
       <c r="O39">
-        <v>1.459577131</v>
+        <v>1.452757594</v>
       </c>
       <c r="P39">
-        <v>6.222407769</v>
+        <v>6.193335006</v>
       </c>
       <c r="Q39">
-        <v>9.012407769000001</v>
+        <v>8.983335006000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1417592294535961</v>
+        <v>0.1431076869139876</v>
       </c>
       <c r="T39">
-        <v>1.757526986932037</v>
+        <v>1.782224458877808</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.784561410483963</v>
+        <v>6.606020320734384</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1054403058866723</v>
+        <v>0.1052985872175791</v>
       </c>
       <c r="C40">
-        <v>44.66414779795871</v>
+        <v>44.10575084415456</v>
       </c>
       <c r="D40">
-        <v>67.9721477979587</v>
+        <v>68.07475084415455</v>
       </c>
       <c r="E40">
-        <v>25.118</v>
+        <v>25.779</v>
       </c>
       <c r="F40">
-        <v>25.118</v>
+        <v>25.779</v>
       </c>
       <c r="G40">
         <v>1.81</v>
@@ -4567,28 +4567,28 @@
         <v>9.01</v>
       </c>
       <c r="M40">
-        <v>1.3639074</v>
+        <v>1.3997997</v>
       </c>
       <c r="N40">
-        <v>7.646092599999999</v>
+        <v>7.6102003</v>
       </c>
       <c r="O40">
-        <v>1.452757594</v>
+        <v>1.445938057</v>
       </c>
       <c r="P40">
-        <v>6.193335006</v>
+        <v>6.164262243</v>
       </c>
       <c r="Q40">
-        <v>8.983335006000001</v>
+        <v>8.954262243000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1431076869139876</v>
+        <v>0.144500356094392</v>
       </c>
       <c r="T40">
-        <v>1.782224458877808</v>
+        <v>1.807731684002128</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.606020320734384</v>
+        <v>6.436635184305297</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1052985872175791</v>
+        <v>0.1051568685484859</v>
       </c>
       <c r="C41">
-        <v>44.10575084415456</v>
+        <v>43.54766411447604</v>
       </c>
       <c r="D41">
-        <v>68.07475084415455</v>
+        <v>68.17766411447603</v>
       </c>
       <c r="E41">
-        <v>25.779</v>
+        <v>26.44</v>
       </c>
       <c r="F41">
-        <v>25.779</v>
+        <v>26.44</v>
       </c>
       <c r="G41">
         <v>1.81</v>
@@ -4649,28 +4649,28 @@
         <v>9.01</v>
       </c>
       <c r="M41">
-        <v>1.3997997</v>
+        <v>1.435692</v>
       </c>
       <c r="N41">
-        <v>7.6102003</v>
+        <v>7.574308</v>
       </c>
       <c r="O41">
-        <v>1.445938057</v>
+        <v>1.43911852</v>
       </c>
       <c r="P41">
-        <v>6.164262243</v>
+        <v>6.13518948</v>
       </c>
       <c r="Q41">
-        <v>8.954262243000001</v>
+        <v>8.92518948</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.144500356094392</v>
+        <v>0.1459394475808098</v>
       </c>
       <c r="T41">
-        <v>1.807731684002128</v>
+        <v>1.834089149963926</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.436635184305297</v>
+        <v>6.275719304697665</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1051568685484859</v>
+        <v>0.1050151498793927</v>
       </c>
       <c r="C42">
-        <v>43.54766411447604</v>
+        <v>42.98988901801464</v>
       </c>
       <c r="D42">
-        <v>68.17766411447603</v>
+        <v>68.28088901801463</v>
       </c>
       <c r="E42">
-        <v>26.44</v>
+        <v>27.101</v>
       </c>
       <c r="F42">
-        <v>26.44</v>
+        <v>27.101</v>
       </c>
       <c r="G42">
         <v>1.81</v>
@@ -4731,28 +4731,28 @@
         <v>9.01</v>
       </c>
       <c r="M42">
-        <v>1.435692</v>
+        <v>1.4715843</v>
       </c>
       <c r="N42">
-        <v>7.574308</v>
+        <v>7.5384157</v>
       </c>
       <c r="O42">
-        <v>1.43911852</v>
+        <v>1.432298983</v>
       </c>
       <c r="P42">
-        <v>6.13518948</v>
+        <v>6.106116717</v>
       </c>
       <c r="Q42">
-        <v>8.92518948</v>
+        <v>8.896116717000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1459394475808098</v>
+        <v>0.1474273218294792</v>
       </c>
       <c r="T42">
-        <v>1.834089149963926</v>
+        <v>1.861340089348158</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.275719304697665</v>
+        <v>6.122652980192844</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1050151498793927</v>
+        <v>0.1052136312102995</v>
       </c>
       <c r="C43">
-        <v>42.98988901801464</v>
+        <v>42.18440686852429</v>
       </c>
       <c r="D43">
-        <v>68.28088901801463</v>
+        <v>68.13640686852429</v>
       </c>
       <c r="E43">
-        <v>27.101</v>
+        <v>27.762</v>
       </c>
       <c r="F43">
-        <v>27.101</v>
+        <v>27.762</v>
       </c>
       <c r="G43">
         <v>1.81</v>
@@ -4813,45 +4813,45 @@
         <v>9.01</v>
       </c>
       <c r="M43">
-        <v>1.4715843</v>
+        <v>1.5352386</v>
       </c>
       <c r="N43">
-        <v>7.5384157</v>
+        <v>7.4747614</v>
       </c>
       <c r="O43">
-        <v>1.432298983</v>
+        <v>1.420204666</v>
       </c>
       <c r="P43">
-        <v>6.106116717</v>
+        <v>6.054556734</v>
       </c>
       <c r="Q43">
-        <v>8.896116717000002</v>
+        <v>8.844556734000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1474273218294792</v>
+        <v>0.1489665020867233</v>
       </c>
       <c r="T43">
-        <v>1.861340089348158</v>
+        <v>1.889530716297363</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.19</v>
       </c>
       <c r="W43">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.122652980192844</v>
+        <v>5.868794596488129</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1052136312102995</v>
+        <v>0.1050800125412063</v>
       </c>
       <c r="C44">
-        <v>42.18440686852429</v>
+        <v>41.62060565136159</v>
       </c>
       <c r="D44">
-        <v>68.13640686852429</v>
+        <v>68.23360565136159</v>
       </c>
       <c r="E44">
-        <v>27.762</v>
+        <v>28.423</v>
       </c>
       <c r="F44">
-        <v>27.762</v>
+        <v>28.423</v>
       </c>
       <c r="G44">
         <v>1.81</v>
@@ -4895,28 +4895,28 @@
         <v>9.01</v>
       </c>
       <c r="M44">
-        <v>1.5352386</v>
+        <v>1.5717919</v>
       </c>
       <c r="N44">
-        <v>7.4747614</v>
+        <v>7.4382081</v>
       </c>
       <c r="O44">
-        <v>1.420204666</v>
+        <v>1.413259539</v>
       </c>
       <c r="P44">
-        <v>6.054556734</v>
+        <v>6.024948561</v>
       </c>
       <c r="Q44">
-        <v>8.844556734000001</v>
+        <v>8.814948561000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1489665020867232</v>
+        <v>0.1505596886687829</v>
       </c>
       <c r="T44">
-        <v>1.889530716297363</v>
+        <v>1.918710488051804</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.868794596488129</v>
+        <v>5.732311001220963</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1050800125412063</v>
+        <v>0.1049463938721131</v>
       </c>
       <c r="C45">
-        <v>41.62060565136159</v>
+        <v>41.05708214476167</v>
       </c>
       <c r="D45">
-        <v>68.23360565136159</v>
+        <v>68.33108214476167</v>
       </c>
       <c r="E45">
-        <v>28.423</v>
+        <v>29.084</v>
       </c>
       <c r="F45">
-        <v>28.423</v>
+        <v>29.084</v>
       </c>
       <c r="G45">
         <v>1.81</v>
@@ -4977,28 +4977,28 @@
         <v>9.01</v>
       </c>
       <c r="M45">
-        <v>1.5717919</v>
+        <v>1.6083452</v>
       </c>
       <c r="N45">
-        <v>7.4382081</v>
+        <v>7.4016548</v>
       </c>
       <c r="O45">
-        <v>1.413259539</v>
+        <v>1.406314412</v>
       </c>
       <c r="P45">
-        <v>6.024948561</v>
+        <v>5.995340388000001</v>
       </c>
       <c r="Q45">
-        <v>8.814948561000001</v>
+        <v>8.785340388000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1505596886687829</v>
+        <v>0.1522097747716305</v>
       </c>
       <c r="T45">
-        <v>1.918710488051804</v>
+        <v>1.94893239451176</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.732311001220963</v>
+        <v>5.602031205738669</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1049463938721131</v>
+        <v>0.1048127752030199</v>
       </c>
       <c r="C46">
-        <v>41.05708214476167</v>
+        <v>40.49383754061433</v>
       </c>
       <c r="D46">
-        <v>68.33108214476167</v>
+        <v>68.42883754061432</v>
       </c>
       <c r="E46">
-        <v>29.084</v>
+        <v>29.745</v>
       </c>
       <c r="F46">
-        <v>29.084</v>
+        <v>29.745</v>
       </c>
       <c r="G46">
         <v>1.81</v>
@@ -5059,28 +5059,28 @@
         <v>9.01</v>
       </c>
       <c r="M46">
-        <v>1.6083452</v>
+        <v>1.6448985</v>
       </c>
       <c r="N46">
-        <v>7.4016548</v>
+        <v>7.3651015</v>
       </c>
       <c r="O46">
-        <v>1.406314412</v>
+        <v>1.399369285</v>
       </c>
       <c r="P46">
-        <v>5.995340388000001</v>
+        <v>5.965732215</v>
       </c>
       <c r="Q46">
-        <v>8.785340388000002</v>
+        <v>8.755732215000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1522097747716305</v>
+        <v>0.1539198640054907</v>
       </c>
       <c r="T46">
-        <v>1.94893239451176</v>
+        <v>1.980253279388442</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.602031205738669</v>
+        <v>5.47754162338892</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1048127752030199</v>
+        <v>0.1046791565339267</v>
       </c>
       <c r="C47">
-        <v>40.49383754061433</v>
+        <v>39.93087303763965</v>
       </c>
       <c r="D47">
-        <v>68.42883754061432</v>
+        <v>68.52687303763965</v>
       </c>
       <c r="E47">
-        <v>29.745</v>
+        <v>30.406</v>
       </c>
       <c r="F47">
-        <v>29.745</v>
+        <v>30.406</v>
       </c>
       <c r="G47">
         <v>1.81</v>
@@ -5141,28 +5141,28 @@
         <v>9.01</v>
       </c>
       <c r="M47">
-        <v>1.6448985</v>
+        <v>1.6814518</v>
       </c>
       <c r="N47">
-        <v>7.3651015</v>
+        <v>7.3285482</v>
       </c>
       <c r="O47">
-        <v>1.399369285</v>
+        <v>1.392424158</v>
       </c>
       <c r="P47">
-        <v>5.965732215</v>
+        <v>5.936124042</v>
       </c>
       <c r="Q47">
-        <v>8.755732215000002</v>
+        <v>8.726124042000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1539198640054907</v>
+        <v>0.155693289877642</v>
       </c>
       <c r="T47">
-        <v>1.980253279388442</v>
+        <v>2.012734197038335</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.47754162338892</v>
+        <v>5.358464631576117</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1046791565339267</v>
+        <v>0.1045455378648335</v>
       </c>
       <c r="C48">
-        <v>39.93087303763965</v>
+        <v>39.36818984143701</v>
       </c>
       <c r="D48">
-        <v>68.52687303763965</v>
+        <v>68.62518984143701</v>
       </c>
       <c r="E48">
-        <v>30.406</v>
+        <v>31.067</v>
       </c>
       <c r="F48">
-        <v>30.406</v>
+        <v>31.067</v>
       </c>
       <c r="G48">
         <v>1.81</v>
@@ -5223,28 +5223,28 @@
         <v>9.01</v>
       </c>
       <c r="M48">
-        <v>1.6814518</v>
+        <v>1.7180051</v>
       </c>
       <c r="N48">
-        <v>7.3285482</v>
+        <v>7.2919949</v>
       </c>
       <c r="O48">
-        <v>1.392424158</v>
+        <v>1.385479031</v>
       </c>
       <c r="P48">
-        <v>5.936124042</v>
+        <v>5.906515869</v>
       </c>
       <c r="Q48">
-        <v>8.726124042000002</v>
+        <v>8.696515869000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.155693289877642</v>
+        <v>0.1575336374808178</v>
       </c>
       <c r="T48">
-        <v>2.012734197038335</v>
+        <v>2.046440809693883</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.358464631576117</v>
+        <v>5.244454745797902</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1045455378648335</v>
+        <v>0.1044119191957403</v>
       </c>
       <c r="C49">
-        <v>39.36818984143701</v>
+        <v>38.80578916453452</v>
       </c>
       <c r="D49">
-        <v>68.62518984143701</v>
+        <v>68.72378916453452</v>
       </c>
       <c r="E49">
-        <v>31.067</v>
+        <v>31.728</v>
       </c>
       <c r="F49">
-        <v>31.067</v>
+        <v>31.728</v>
       </c>
       <c r="G49">
         <v>1.81</v>
@@ -5305,28 +5305,28 @@
         <v>9.01</v>
       </c>
       <c r="M49">
-        <v>1.7180051</v>
+        <v>1.7545584</v>
       </c>
       <c r="N49">
-        <v>7.2919949</v>
+        <v>7.255441599999999</v>
       </c>
       <c r="O49">
-        <v>1.385479031</v>
+        <v>1.378533904</v>
       </c>
       <c r="P49">
-        <v>5.906515869</v>
+        <v>5.876907695999999</v>
       </c>
       <c r="Q49">
-        <v>8.696515869000001</v>
+        <v>8.666907695999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1575336374808178</v>
+        <v>0.1594447676841159</v>
       </c>
       <c r="T49">
-        <v>2.046440809693883</v>
+        <v>2.081443830528492</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.244454745797902</v>
+        <v>5.135195271927112</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1044119191957402</v>
+        <v>0.104278300526647</v>
       </c>
       <c r="C50">
-        <v>38.80578916453453</v>
+        <v>38.2436722264389</v>
       </c>
       <c r="D50">
-        <v>68.72378916453452</v>
+        <v>68.8226722264389</v>
       </c>
       <c r="E50">
-        <v>31.72799999999999</v>
+        <v>32.389</v>
       </c>
       <c r="F50">
-        <v>31.72799999999999</v>
+        <v>32.389</v>
       </c>
       <c r="G50">
         <v>1.81</v>
@@ -5387,28 +5387,28 @@
         <v>9.01</v>
       </c>
       <c r="M50">
-        <v>1.7545584</v>
+        <v>1.7911117</v>
       </c>
       <c r="N50">
-        <v>7.2554416</v>
+        <v>7.2188883</v>
       </c>
       <c r="O50">
-        <v>1.378533904</v>
+        <v>1.371588777</v>
       </c>
       <c r="P50">
-        <v>5.876907696</v>
+        <v>5.847299523</v>
       </c>
       <c r="Q50">
-        <v>8.666907696000001</v>
+        <v>8.637299523000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1594447676841159</v>
+        <v>0.1614308441698961</v>
       </c>
       <c r="T50">
-        <v>2.081443830528491</v>
+        <v>2.11781951884681</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.135195271927113</v>
+        <v>5.030395368418397</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.104278300526647</v>
+        <v>0.1041446818575538</v>
       </c>
       <c r="C51">
-        <v>38.2436722264389</v>
+        <v>37.68184025368562</v>
       </c>
       <c r="D51">
-        <v>68.8226722264389</v>
+        <v>68.92184025368562</v>
       </c>
       <c r="E51">
-        <v>32.389</v>
+        <v>33.05</v>
       </c>
       <c r="F51">
-        <v>32.389</v>
+        <v>33.05</v>
       </c>
       <c r="G51">
         <v>1.81</v>
@@ -5469,28 +5469,28 @@
         <v>9.01</v>
       </c>
       <c r="M51">
-        <v>1.7911117</v>
+        <v>1.827665</v>
       </c>
       <c r="N51">
-        <v>7.2188883</v>
+        <v>7.182335</v>
       </c>
       <c r="O51">
-        <v>1.371588777</v>
+        <v>1.36464365</v>
       </c>
       <c r="P51">
-        <v>5.847299523</v>
+        <v>5.81769135</v>
       </c>
       <c r="Q51">
-        <v>8.637299523000001</v>
+        <v>8.607691350000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1614308441698961</v>
+        <v>0.1634963637151077</v>
       </c>
       <c r="T51">
-        <v>2.11781951884681</v>
+        <v>2.155650234697861</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.030395368418397</v>
+        <v>4.929787461050029</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1041446818575538</v>
+        <v>0.1040110631884606</v>
       </c>
       <c r="C52">
-        <v>37.68184025368562</v>
+        <v>37.12029447988985</v>
       </c>
       <c r="D52">
-        <v>68.92184025368562</v>
+        <v>69.02129447988985</v>
       </c>
       <c r="E52">
-        <v>33.05</v>
+        <v>33.711</v>
       </c>
       <c r="F52">
-        <v>33.05</v>
+        <v>33.711</v>
       </c>
       <c r="G52">
         <v>1.81</v>
@@ -5551,28 +5551,28 @@
         <v>9.01</v>
       </c>
       <c r="M52">
-        <v>1.827665</v>
+        <v>1.8642183</v>
       </c>
       <c r="N52">
-        <v>7.182335</v>
+        <v>7.1457817</v>
       </c>
       <c r="O52">
-        <v>1.36464365</v>
+        <v>1.357698523</v>
       </c>
       <c r="P52">
-        <v>5.81769135</v>
+        <v>5.788083177</v>
       </c>
       <c r="Q52">
-        <v>8.607691350000001</v>
+        <v>8.578083177</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1634963637151077</v>
+        <v>0.1656461901805319</v>
       </c>
       <c r="T52">
-        <v>2.155650234697861</v>
+        <v>2.195025061399976</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.929787461050029</v>
+        <v>4.833124961813754</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1040110631884606</v>
+        <v>0.1038774445193674</v>
       </c>
       <c r="C53">
-        <v>37.12029447988985</v>
+        <v>36.55903614579735</v>
       </c>
       <c r="D53">
-        <v>69.02129447988985</v>
+        <v>69.12103614579735</v>
       </c>
       <c r="E53">
-        <v>33.711</v>
+        <v>34.372</v>
       </c>
       <c r="F53">
-        <v>33.711</v>
+        <v>34.372</v>
       </c>
       <c r="G53">
         <v>1.81</v>
@@ -5633,28 +5633,28 @@
         <v>9.01</v>
       </c>
       <c r="M53">
-        <v>1.8642183</v>
+        <v>1.9007716</v>
       </c>
       <c r="N53">
-        <v>7.1457817</v>
+        <v>7.109228399999999</v>
       </c>
       <c r="O53">
-        <v>1.357698523</v>
+        <v>1.350753396</v>
       </c>
       <c r="P53">
-        <v>5.788083177</v>
+        <v>5.758475003999999</v>
       </c>
       <c r="Q53">
-        <v>8.578083177</v>
+        <v>8.548475004</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1656461901805319</v>
+        <v>0.1678855927486821</v>
       </c>
       <c r="T53">
-        <v>2.195025061399976</v>
+        <v>2.236040505881345</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.833124961813754</v>
+        <v>4.740180251009642</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1038774445193674</v>
+        <v>0.1037438258502742</v>
       </c>
       <c r="C54">
-        <v>36.55903614579735</v>
+        <v>35.99806649933628</v>
       </c>
       <c r="D54">
-        <v>69.12103614579735</v>
+        <v>69.22106649933627</v>
       </c>
       <c r="E54">
-        <v>34.372</v>
+        <v>35.033</v>
       </c>
       <c r="F54">
-        <v>34.372</v>
+        <v>35.033</v>
       </c>
       <c r="G54">
         <v>1.81</v>
@@ -5715,28 +5715,28 @@
         <v>9.01</v>
       </c>
       <c r="M54">
-        <v>1.9007716</v>
+        <v>1.9373249</v>
       </c>
       <c r="N54">
-        <v>7.109228399999999</v>
+        <v>7.0726751</v>
       </c>
       <c r="O54">
-        <v>1.350753396</v>
+        <v>1.343808269</v>
       </c>
       <c r="P54">
-        <v>5.758475003999999</v>
+        <v>5.728866830999999</v>
       </c>
       <c r="Q54">
-        <v>8.548475004</v>
+        <v>8.518866831</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1678855927486821</v>
+        <v>0.1702202890431366</v>
       </c>
       <c r="T54">
-        <v>2.236040505881345</v>
+        <v>2.278801288425751</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.740180251009642</v>
+        <v>4.650742887783045</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1037438258502742</v>
+        <v>0.103610207181181</v>
       </c>
       <c r="C55">
-        <v>35.99806649933628</v>
+        <v>35.4373867956691</v>
       </c>
       <c r="D55">
-        <v>69.22106649933627</v>
+        <v>69.3213867956691</v>
       </c>
       <c r="E55">
-        <v>35.033</v>
+        <v>35.694</v>
       </c>
       <c r="F55">
-        <v>35.033</v>
+        <v>35.694</v>
       </c>
       <c r="G55">
         <v>1.81</v>
@@ -5797,28 +5797,28 @@
         <v>9.01</v>
       </c>
       <c r="M55">
-        <v>1.9373249</v>
+        <v>1.9738782</v>
       </c>
       <c r="N55">
-        <v>7.0726751</v>
+        <v>7.0361218</v>
       </c>
       <c r="O55">
-        <v>1.343808269</v>
+        <v>1.336863142</v>
       </c>
       <c r="P55">
-        <v>5.728866830999999</v>
+        <v>5.699258658</v>
       </c>
       <c r="Q55">
-        <v>8.518866831</v>
+        <v>8.489258658000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1702202890431366</v>
+        <v>0.1726564938721326</v>
       </c>
       <c r="T55">
-        <v>2.278801288425751</v>
+        <v>2.32342123542861</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.650742887783045</v>
+        <v>4.564618019490767</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.103610207181181</v>
+        <v>0.1045903385120878</v>
       </c>
       <c r="C56">
-        <v>35.4373867956691</v>
+        <v>34.04719404024504</v>
       </c>
       <c r="D56">
-        <v>69.3213867956691</v>
+        <v>68.59219404024503</v>
       </c>
       <c r="E56">
-        <v>35.694</v>
+        <v>36.355</v>
       </c>
       <c r="F56">
-        <v>35.694</v>
+        <v>36.355</v>
       </c>
       <c r="G56">
         <v>1.81</v>
@@ -5879,45 +5879,45 @@
         <v>9.01</v>
       </c>
       <c r="M56">
-        <v>1.9738782</v>
+        <v>2.101319</v>
       </c>
       <c r="N56">
-        <v>7.0361218</v>
+        <v>6.908681</v>
       </c>
       <c r="O56">
-        <v>1.336863142</v>
+        <v>1.31264939</v>
       </c>
       <c r="P56">
-        <v>5.699258658</v>
+        <v>5.59603161</v>
       </c>
       <c r="Q56">
-        <v>8.489258658000001</v>
+        <v>8.38603161</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1726564938721326</v>
+        <v>0.1752009744713063</v>
       </c>
       <c r="T56">
-        <v>2.32342123542861</v>
+        <v>2.370024291187152</v>
       </c>
       <c r="U56">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V56">
         <v>0.19</v>
       </c>
       <c r="W56">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.564618019490767</v>
+        <v>4.287783054357762</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1045903385120878</v>
+        <v>0.1044769698429946</v>
       </c>
       <c r="C57">
-        <v>34.04719404024504</v>
+        <v>33.46975189896167</v>
       </c>
       <c r="D57">
-        <v>68.59219404024503</v>
+        <v>68.67575189896166</v>
       </c>
       <c r="E57">
-        <v>36.355</v>
+        <v>37.016</v>
       </c>
       <c r="F57">
-        <v>36.355</v>
+        <v>37.016</v>
       </c>
       <c r="G57">
         <v>1.81</v>
@@ -5961,28 +5961,28 @@
         <v>9.01</v>
       </c>
       <c r="M57">
-        <v>2.101319</v>
+        <v>2.1395248</v>
       </c>
       <c r="N57">
-        <v>6.908681</v>
+        <v>6.8704752</v>
       </c>
       <c r="O57">
-        <v>1.31264939</v>
+        <v>1.305390288</v>
       </c>
       <c r="P57">
-        <v>5.59603161</v>
+        <v>5.565084912</v>
       </c>
       <c r="Q57">
-        <v>8.38603161</v>
+        <v>8.355084912000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1752009744713063</v>
+        <v>0.1778611132795332</v>
       </c>
       <c r="T57">
-        <v>2.370024291187152</v>
+        <v>2.41874566766199</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.287783054357762</v>
+        <v>4.211215499815659</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1044769698429946</v>
+        <v>0.1043636011739014</v>
       </c>
       <c r="C58">
-        <v>33.46975189896167</v>
+        <v>32.89251358353567</v>
       </c>
       <c r="D58">
-        <v>68.67575189896166</v>
+        <v>68.75951358353566</v>
       </c>
       <c r="E58">
-        <v>37.016</v>
+        <v>37.677</v>
       </c>
       <c r="F58">
-        <v>37.016</v>
+        <v>37.677</v>
       </c>
       <c r="G58">
         <v>1.81</v>
@@ -6043,28 +6043,28 @@
         <v>9.01</v>
       </c>
       <c r="M58">
-        <v>2.1395248</v>
+        <v>2.1777306</v>
       </c>
       <c r="N58">
-        <v>6.8704752</v>
+        <v>6.832269399999999</v>
       </c>
       <c r="O58">
-        <v>1.305390288</v>
+        <v>1.298131186</v>
       </c>
       <c r="P58">
-        <v>5.565084912</v>
+        <v>5.534138214</v>
       </c>
       <c r="Q58">
-        <v>8.355084912000001</v>
+        <v>8.324138214000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1778611132795332</v>
+        <v>0.1806449794741893</v>
       </c>
       <c r="T58">
-        <v>2.41874566766199</v>
+        <v>2.469733154670542</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.211215499815659</v>
+        <v>4.137334526134683</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1043636011739014</v>
+        <v>0.1042502325048082</v>
       </c>
       <c r="C59">
-        <v>32.89251358353567</v>
+        <v>32.31547984067797</v>
       </c>
       <c r="D59">
-        <v>68.75951358353566</v>
+        <v>68.84347984067797</v>
       </c>
       <c r="E59">
-        <v>37.677</v>
+        <v>38.338</v>
       </c>
       <c r="F59">
-        <v>37.677</v>
+        <v>38.338</v>
       </c>
       <c r="G59">
         <v>1.81</v>
@@ -6125,28 +6125,28 @@
         <v>9.01</v>
       </c>
       <c r="M59">
-        <v>2.1777306</v>
+        <v>2.2159364</v>
       </c>
       <c r="N59">
-        <v>6.832269399999999</v>
+        <v>6.794063599999999</v>
       </c>
       <c r="O59">
-        <v>1.298131186</v>
+        <v>1.290872084</v>
       </c>
       <c r="P59">
-        <v>5.534138214</v>
+        <v>5.503191515999999</v>
       </c>
       <c r="Q59">
-        <v>8.324138214000001</v>
+        <v>8.293191516</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1806449794741893</v>
+        <v>0.1835614107257338</v>
       </c>
       <c r="T59">
-        <v>2.469733154670542</v>
+        <v>2.523148617250931</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.137334526134683</v>
+        <v>4.066001172235809</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1042502325048082</v>
+        <v>0.105809513835715</v>
       </c>
       <c r="C60">
-        <v>32.31547984067799</v>
+        <v>30.51729135014965</v>
       </c>
       <c r="D60">
-        <v>68.84347984067799</v>
+        <v>67.70629135014964</v>
       </c>
       <c r="E60">
-        <v>38.33799999999999</v>
+        <v>38.999</v>
       </c>
       <c r="F60">
-        <v>38.33799999999999</v>
+        <v>38.999</v>
       </c>
       <c r="G60">
         <v>1.81</v>
@@ -6207,45 +6207,45 @@
         <v>9.01</v>
       </c>
       <c r="M60">
-        <v>2.2159364</v>
+        <v>2.3906387</v>
       </c>
       <c r="N60">
-        <v>6.794063599999999</v>
+        <v>6.6193613</v>
       </c>
       <c r="O60">
-        <v>1.290872084</v>
+        <v>1.257678647</v>
       </c>
       <c r="P60">
-        <v>5.503191515999999</v>
+        <v>5.361682653</v>
       </c>
       <c r="Q60">
-        <v>8.293191516</v>
+        <v>8.151682653000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1835614107257337</v>
+        <v>0.186620106916378</v>
       </c>
       <c r="T60">
-        <v>2.523148617250929</v>
+        <v>2.579169712152312</v>
       </c>
       <c r="U60">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V60">
         <v>0.19</v>
       </c>
       <c r="W60">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.06600117223581</v>
+        <v>3.768867290569671</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.105809513835715</v>
+        <v>0.1057244951666218</v>
       </c>
       <c r="C61">
-        <v>30.51729135014965</v>
+        <v>29.91732647205468</v>
       </c>
       <c r="D61">
-        <v>67.70629135014964</v>
+        <v>67.76732647205468</v>
       </c>
       <c r="E61">
-        <v>38.999</v>
+        <v>39.66</v>
       </c>
       <c r="F61">
-        <v>38.999</v>
+        <v>39.66</v>
       </c>
       <c r="G61">
         <v>1.81</v>
@@ -6289,28 +6289,28 @@
         <v>9.01</v>
       </c>
       <c r="M61">
-        <v>2.3906387</v>
+        <v>2.431158</v>
       </c>
       <c r="N61">
-        <v>6.6193613</v>
+        <v>6.578842</v>
       </c>
       <c r="O61">
-        <v>1.257678647</v>
+        <v>1.24997998</v>
       </c>
       <c r="P61">
-        <v>5.361682653</v>
+        <v>5.32886202</v>
       </c>
       <c r="Q61">
-        <v>8.151682653000002</v>
+        <v>8.118862020000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.186620106916378</v>
+        <v>0.1898317379165544</v>
       </c>
       <c r="T61">
-        <v>2.579169712152312</v>
+        <v>2.637991861798763</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.768867290569671</v>
+        <v>3.706052835726843</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1057244951666218</v>
+        <v>0.1056394764975286</v>
       </c>
       <c r="C62">
-        <v>29.91732647205468</v>
+        <v>29.31747173578826</v>
       </c>
       <c r="D62">
-        <v>67.76732647205468</v>
+        <v>67.82847173578826</v>
       </c>
       <c r="E62">
-        <v>39.66</v>
+        <v>40.321</v>
       </c>
       <c r="F62">
-        <v>39.66</v>
+        <v>40.321</v>
       </c>
       <c r="G62">
         <v>1.81</v>
@@ -6371,28 +6371,28 @@
         <v>9.01</v>
       </c>
       <c r="M62">
-        <v>2.431158</v>
+        <v>2.4716773</v>
       </c>
       <c r="N62">
-        <v>6.578842</v>
+        <v>6.5383227</v>
       </c>
       <c r="O62">
-        <v>1.24997998</v>
+        <v>1.242281313</v>
       </c>
       <c r="P62">
-        <v>5.32886202</v>
+        <v>5.296041387</v>
       </c>
       <c r="Q62">
-        <v>8.118862020000002</v>
+        <v>8.086041387000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1898317379165544</v>
+        <v>0.1932080679423809</v>
       </c>
       <c r="T62">
-        <v>2.637991861798763</v>
+        <v>2.699830531939905</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.706052835726843</v>
+        <v>3.645297871206731</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1056394764975286</v>
+        <v>0.1055544578284354</v>
       </c>
       <c r="C63">
-        <v>29.31747173578826</v>
+        <v>28.7177274397567</v>
       </c>
       <c r="D63">
-        <v>67.82847173578826</v>
+        <v>67.8897274397567</v>
       </c>
       <c r="E63">
-        <v>40.321</v>
+        <v>40.982</v>
       </c>
       <c r="F63">
-        <v>40.321</v>
+        <v>40.982</v>
       </c>
       <c r="G63">
         <v>1.81</v>
@@ -6453,28 +6453,28 @@
         <v>9.01</v>
       </c>
       <c r="M63">
-        <v>2.4716773</v>
+        <v>2.5121966</v>
       </c>
       <c r="N63">
-        <v>6.5383227</v>
+        <v>6.4978034</v>
       </c>
       <c r="O63">
-        <v>1.242281313</v>
+        <v>1.234582646</v>
       </c>
       <c r="P63">
-        <v>5.296041387</v>
+        <v>5.263220754000001</v>
       </c>
       <c r="Q63">
-        <v>8.086041387000002</v>
+        <v>8.053220754000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1932080679423809</v>
+        <v>0.1967620995485141</v>
       </c>
       <c r="T63">
-        <v>2.699830531939905</v>
+        <v>2.76492386893058</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.645297871206731</v>
+        <v>3.586502744251784</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1055544578284354</v>
+        <v>0.1054694391593421</v>
       </c>
       <c r="C64">
-        <v>28.7177274397567</v>
+        <v>28.11809388344529</v>
       </c>
       <c r="D64">
-        <v>67.8897274397567</v>
+        <v>67.95109388344528</v>
       </c>
       <c r="E64">
-        <v>40.982</v>
+        <v>41.64299999999999</v>
       </c>
       <c r="F64">
-        <v>40.982</v>
+        <v>41.64299999999999</v>
       </c>
       <c r="G64">
         <v>1.81</v>
@@ -6535,28 +6535,28 @@
         <v>9.01</v>
       </c>
       <c r="M64">
-        <v>2.5121966</v>
+        <v>2.552715899999999</v>
       </c>
       <c r="N64">
-        <v>6.4978034</v>
+        <v>6.457284100000001</v>
       </c>
       <c r="O64">
-        <v>1.234582646</v>
+        <v>1.226883979</v>
       </c>
       <c r="P64">
-        <v>5.263220754000001</v>
+        <v>5.230400121000001</v>
       </c>
       <c r="Q64">
-        <v>8.053220754000002</v>
+        <v>8.020400121000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1967620995485141</v>
+        <v>0.200508240971195</v>
       </c>
       <c r="T64">
-        <v>2.76492386893058</v>
+        <v>2.833535764677508</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.586502744251784</v>
+        <v>3.529574129263661</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1054694391593421</v>
+        <v>0.1068359404902489</v>
       </c>
       <c r="C65">
-        <v>28.11809388344529</v>
+        <v>26.48399982341758</v>
       </c>
       <c r="D65">
-        <v>67.95109388344528</v>
+        <v>66.97799982341758</v>
       </c>
       <c r="E65">
-        <v>41.64299999999999</v>
+        <v>42.30399999999999</v>
       </c>
       <c r="F65">
-        <v>41.64299999999999</v>
+        <v>42.30399999999999</v>
       </c>
       <c r="G65">
         <v>1.81</v>
@@ -6617,45 +6617,45 @@
         <v>9.01</v>
       </c>
       <c r="M65">
-        <v>2.552715899999999</v>
+        <v>2.7116864</v>
       </c>
       <c r="N65">
-        <v>6.457284100000001</v>
+        <v>6.2983136</v>
       </c>
       <c r="O65">
-        <v>1.226883979</v>
+        <v>1.196679584</v>
       </c>
       <c r="P65">
-        <v>5.230400121000001</v>
+        <v>5.101634016</v>
       </c>
       <c r="Q65">
-        <v>8.020400121000002</v>
+        <v>7.891634016000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.200508240971195</v>
+        <v>0.2044625013618026</v>
       </c>
       <c r="T65">
-        <v>2.833535764677508</v>
+        <v>2.905959432410377</v>
       </c>
       <c r="U65">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V65">
         <v>0.19</v>
       </c>
       <c r="W65">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.529574129263661</v>
+        <v>3.322655599113526</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1068359404902489</v>
+        <v>0.1067736018211557</v>
       </c>
       <c r="C66">
-        <v>26.48399982341758</v>
+        <v>25.86678446741683</v>
       </c>
       <c r="D66">
-        <v>66.97799982341758</v>
+        <v>67.02178446741682</v>
       </c>
       <c r="E66">
-        <v>42.30399999999999</v>
+        <v>42.965</v>
       </c>
       <c r="F66">
-        <v>42.30399999999999</v>
+        <v>42.965</v>
       </c>
       <c r="G66">
         <v>1.81</v>
@@ -6699,28 +6699,28 @@
         <v>9.01</v>
       </c>
       <c r="M66">
-        <v>2.7116864</v>
+        <v>2.7540565</v>
       </c>
       <c r="N66">
-        <v>6.2983136</v>
+        <v>6.2559435</v>
       </c>
       <c r="O66">
-        <v>1.196679584</v>
+        <v>1.188629265</v>
       </c>
       <c r="P66">
-        <v>5.101634016</v>
+        <v>5.067314235</v>
       </c>
       <c r="Q66">
-        <v>7.891634016000001</v>
+        <v>7.857314235</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2044625013618026</v>
+        <v>0.2086427194890164</v>
       </c>
       <c r="T66">
-        <v>2.905959432410377</v>
+        <v>2.982521595442266</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.322655599113526</v>
+        <v>3.271537820665626</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1067736018211557</v>
+        <v>0.1067112631520625</v>
       </c>
       <c r="C67">
-        <v>25.86678446741683</v>
+        <v>25.24962639437802</v>
       </c>
       <c r="D67">
-        <v>67.02178446741682</v>
+        <v>67.06562639437801</v>
       </c>
       <c r="E67">
-        <v>42.965</v>
+        <v>43.626</v>
       </c>
       <c r="F67">
-        <v>42.965</v>
+        <v>43.626</v>
       </c>
       <c r="G67">
         <v>1.81</v>
@@ -6781,28 +6781,28 @@
         <v>9.01</v>
       </c>
       <c r="M67">
-        <v>2.7540565</v>
+        <v>2.7964266</v>
       </c>
       <c r="N67">
-        <v>6.2559435</v>
+        <v>6.2135734</v>
       </c>
       <c r="O67">
-        <v>1.188629265</v>
+        <v>1.180578946</v>
       </c>
       <c r="P67">
-        <v>5.067314235</v>
+        <v>5.032994454</v>
       </c>
       <c r="Q67">
-        <v>7.857314235</v>
+        <v>7.822994454000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2086427194890164</v>
+        <v>0.2130688328001839</v>
       </c>
       <c r="T67">
-        <v>2.982521595442266</v>
+        <v>3.06358741512309</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.271537820665626</v>
+        <v>3.221969065807055</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1067112631520625</v>
+        <v>0.1066489244829693</v>
       </c>
       <c r="C68">
-        <v>25.24962639437802</v>
+        <v>24.6325257167887</v>
       </c>
       <c r="D68">
-        <v>67.06562639437801</v>
+        <v>67.1095257167887</v>
       </c>
       <c r="E68">
-        <v>43.626</v>
+        <v>44.287</v>
       </c>
       <c r="F68">
-        <v>43.626</v>
+        <v>44.287</v>
       </c>
       <c r="G68">
         <v>1.81</v>
@@ -6863,28 +6863,28 @@
         <v>9.01</v>
       </c>
       <c r="M68">
-        <v>2.7964266</v>
+        <v>2.8387967</v>
       </c>
       <c r="N68">
-        <v>6.2135734</v>
+        <v>6.1712033</v>
       </c>
       <c r="O68">
-        <v>1.180578946</v>
+        <v>1.172528627</v>
       </c>
       <c r="P68">
-        <v>5.032994454</v>
+        <v>4.998674673</v>
       </c>
       <c r="Q68">
-        <v>7.822994454000001</v>
+        <v>7.788674673000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2130688328001839</v>
+        <v>0.2177631954029373</v>
       </c>
       <c r="T68">
-        <v>3.06358741512309</v>
+        <v>3.14956631478457</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.221969065807055</v>
+        <v>3.173879975272622</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1066489244829693</v>
+        <v>0.1065865858138761</v>
       </c>
       <c r="C69">
-        <v>24.6325257167887</v>
+        <v>24.0154825474312</v>
       </c>
       <c r="D69">
-        <v>67.1095257167887</v>
+        <v>67.1534825474312</v>
       </c>
       <c r="E69">
-        <v>44.287</v>
+        <v>44.948</v>
       </c>
       <c r="F69">
-        <v>44.287</v>
+        <v>44.948</v>
       </c>
       <c r="G69">
         <v>1.81</v>
@@ -6945,28 +6945,28 @@
         <v>9.01</v>
       </c>
       <c r="M69">
-        <v>2.8387967</v>
+        <v>2.8811668</v>
       </c>
       <c r="N69">
-        <v>6.1712033</v>
+        <v>6.128833199999999</v>
       </c>
       <c r="O69">
-        <v>1.172528627</v>
+        <v>1.164478308</v>
       </c>
       <c r="P69">
-        <v>4.998674673</v>
+        <v>4.964354891999999</v>
       </c>
       <c r="Q69">
-        <v>7.788674673000001</v>
+        <v>7.754354892</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2177631954029373</v>
+        <v>0.2227509556683629</v>
       </c>
       <c r="T69">
-        <v>3.14956631478457</v>
+        <v>3.240918895674893</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.173879975272622</v>
+        <v>3.127205269753906</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1065865858138761</v>
+        <v>0.1065242471447829</v>
       </c>
       <c r="C70">
-        <v>24.0154825474312</v>
+        <v>23.39849699938346</v>
       </c>
       <c r="D70">
-        <v>67.1534825474312</v>
+        <v>67.19749699938346</v>
       </c>
       <c r="E70">
-        <v>44.948</v>
+        <v>45.609</v>
       </c>
       <c r="F70">
-        <v>44.948</v>
+        <v>45.609</v>
       </c>
       <c r="G70">
         <v>1.81</v>
@@ -7027,28 +7027,28 @@
         <v>9.01</v>
       </c>
       <c r="M70">
-        <v>2.8811668</v>
+        <v>2.9235369</v>
       </c>
       <c r="N70">
-        <v>6.128833199999999</v>
+        <v>6.0864631</v>
       </c>
       <c r="O70">
-        <v>1.164478308</v>
+        <v>1.156427989</v>
       </c>
       <c r="P70">
-        <v>4.964354891999999</v>
+        <v>4.930035111</v>
       </c>
       <c r="Q70">
-        <v>7.754354892</v>
+        <v>7.720035111000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2227509556683629</v>
+        <v>0.2280605069186546</v>
       </c>
       <c r="T70">
-        <v>3.240918895674893</v>
+        <v>3.338165191461365</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.127205269753906</v>
+        <v>3.081883454250227</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1065242471447829</v>
+        <v>0.1064619084756897</v>
       </c>
       <c r="C71">
-        <v>23.39849699938346</v>
+        <v>22.78156918602016</v>
       </c>
       <c r="D71">
-        <v>67.19749699938346</v>
+        <v>67.24156918602016</v>
       </c>
       <c r="E71">
-        <v>45.609</v>
+        <v>46.27</v>
       </c>
       <c r="F71">
-        <v>45.609</v>
+        <v>46.27</v>
       </c>
       <c r="G71">
         <v>1.81</v>
@@ -7109,28 +7109,28 @@
         <v>9.01</v>
       </c>
       <c r="M71">
-        <v>2.9235369</v>
+        <v>2.965907000000001</v>
       </c>
       <c r="N71">
-        <v>6.0864631</v>
+        <v>6.044092999999999</v>
       </c>
       <c r="O71">
-        <v>1.156427989</v>
+        <v>1.14837767</v>
       </c>
       <c r="P71">
-        <v>4.930035111</v>
+        <v>4.89571533</v>
       </c>
       <c r="Q71">
-        <v>7.720035111000001</v>
+        <v>7.685715330000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2280605069186546</v>
+        <v>0.233724028252299</v>
       </c>
       <c r="T71">
-        <v>3.338165191461365</v>
+        <v>3.441894573633602</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.081883454250227</v>
+        <v>3.037856547760937</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1064619084756897</v>
+        <v>0.1108853498065965</v>
       </c>
       <c r="C72">
-        <v>22.78156918602016</v>
+        <v>19.13039288929516</v>
       </c>
       <c r="D72">
-        <v>67.24156918602016</v>
+        <v>64.25139288929516</v>
       </c>
       <c r="E72">
-        <v>46.27</v>
+        <v>46.931</v>
       </c>
       <c r="F72">
-        <v>46.27</v>
+        <v>46.931</v>
       </c>
       <c r="G72">
         <v>1.81</v>
@@ -7191,45 +7191,45 @@
         <v>9.01</v>
       </c>
       <c r="M72">
-        <v>2.965907000000001</v>
+        <v>3.374338900000001</v>
       </c>
       <c r="N72">
-        <v>6.044092999999999</v>
+        <v>5.635661099999999</v>
       </c>
       <c r="O72">
-        <v>1.14837767</v>
+        <v>1.070775609</v>
       </c>
       <c r="P72">
-        <v>4.89571533</v>
+        <v>4.564885490999999</v>
       </c>
       <c r="Q72">
-        <v>7.685715330000001</v>
+        <v>7.354885491</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.233724028252299</v>
+        <v>0.2397781372641259</v>
       </c>
       <c r="T72">
-        <v>3.441894573633602</v>
+        <v>3.552777706300477</v>
       </c>
       <c r="U72">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V72">
         <v>0.19</v>
       </c>
       <c r="W72">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>3.037856547760937</v>
+        <v>2.670152663089056</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1108853498065965</v>
+        <v>0.1108861911375033</v>
       </c>
       <c r="C73">
-        <v>19.13039288929517</v>
+        <v>18.46884945830622</v>
       </c>
       <c r="D73">
-        <v>64.25139288929516</v>
+        <v>64.25084945830621</v>
       </c>
       <c r="E73">
-        <v>46.93099999999999</v>
+        <v>47.59199999999999</v>
       </c>
       <c r="F73">
-        <v>46.93099999999999</v>
+        <v>47.59199999999999</v>
       </c>
       <c r="G73">
         <v>1.81</v>
@@ -7273,28 +7273,28 @@
         <v>9.01</v>
       </c>
       <c r="M73">
-        <v>3.3743389</v>
+        <v>3.4218648</v>
       </c>
       <c r="N73">
-        <v>5.6356611</v>
+        <v>5.5881352</v>
       </c>
       <c r="O73">
-        <v>1.070775609</v>
+        <v>1.061745688</v>
       </c>
       <c r="P73">
-        <v>4.564885491</v>
+        <v>4.526389512</v>
       </c>
       <c r="Q73">
-        <v>7.354885491000001</v>
+        <v>7.316389512000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2397781372641258</v>
+        <v>0.2462646826339403</v>
       </c>
       <c r="T73">
-        <v>3.552777706300476</v>
+        <v>3.671581062729269</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.670152663089057</v>
+        <v>2.633067209435043</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1108861911375033</v>
+        <v>0.1108870324684101</v>
       </c>
       <c r="C74">
-        <v>18.46884945830622</v>
+        <v>17.80730603650972</v>
       </c>
       <c r="D74">
-        <v>64.25084945830621</v>
+        <v>64.25030603650971</v>
       </c>
       <c r="E74">
-        <v>47.59199999999999</v>
+        <v>48.25299999999999</v>
       </c>
       <c r="F74">
-        <v>47.59199999999999</v>
+        <v>48.25299999999999</v>
       </c>
       <c r="G74">
         <v>1.81</v>
@@ -7355,28 +7355,28 @@
         <v>9.01</v>
       </c>
       <c r="M74">
-        <v>3.4218648</v>
+        <v>3.4693907</v>
       </c>
       <c r="N74">
-        <v>5.5881352</v>
+        <v>5.5406093</v>
       </c>
       <c r="O74">
-        <v>1.061745688</v>
+        <v>1.052715767</v>
       </c>
       <c r="P74">
-        <v>4.526389512</v>
+        <v>4.487893532999999</v>
       </c>
       <c r="Q74">
-        <v>7.316389512000001</v>
+        <v>7.277893533</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2462646826339403</v>
+        <v>0.2532317128459632</v>
       </c>
       <c r="T74">
-        <v>3.671581062729269</v>
+        <v>3.799184667782418</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.633067209435043</v>
+        <v>2.596997795607165</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1108870324684101</v>
+        <v>0.1108878737993169</v>
       </c>
       <c r="C75">
-        <v>17.80730603650972</v>
+        <v>17.14576262390548</v>
       </c>
       <c r="D75">
-        <v>64.25030603650971</v>
+        <v>64.24976262390547</v>
       </c>
       <c r="E75">
-        <v>48.25299999999999</v>
+        <v>48.91399999999999</v>
       </c>
       <c r="F75">
-        <v>48.25299999999999</v>
+        <v>48.91399999999999</v>
       </c>
       <c r="G75">
         <v>1.81</v>
@@ -7437,28 +7437,28 @@
         <v>9.01</v>
       </c>
       <c r="M75">
-        <v>3.4693907</v>
+        <v>3.5169166</v>
       </c>
       <c r="N75">
-        <v>5.5406093</v>
+        <v>5.4930834</v>
       </c>
       <c r="O75">
-        <v>1.052715767</v>
+        <v>1.043685846</v>
       </c>
       <c r="P75">
-        <v>4.487893532999999</v>
+        <v>4.449397554</v>
       </c>
       <c r="Q75">
-        <v>7.277893533</v>
+        <v>7.239397554000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2532317128459632</v>
+        <v>0.260734668458911</v>
       </c>
       <c r="T75">
-        <v>3.799184667782418</v>
+        <v>3.936603934762732</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.596997795607165</v>
+        <v>2.561903230801663</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1108878737993169</v>
+        <v>0.1108887151302237</v>
       </c>
       <c r="C76">
-        <v>17.14576262390548</v>
+        <v>16.48421922049325</v>
       </c>
       <c r="D76">
-        <v>64.24976262390547</v>
+        <v>64.24921922049325</v>
       </c>
       <c r="E76">
-        <v>48.91399999999999</v>
+        <v>49.575</v>
       </c>
       <c r="F76">
-        <v>48.91399999999999</v>
+        <v>49.575</v>
       </c>
       <c r="G76">
         <v>1.81</v>
@@ -7519,28 +7519,28 @@
         <v>9.01</v>
       </c>
       <c r="M76">
-        <v>3.5169166</v>
+        <v>3.5644425</v>
       </c>
       <c r="N76">
-        <v>5.4930834</v>
+        <v>5.4455575</v>
       </c>
       <c r="O76">
-        <v>1.043685846</v>
+        <v>1.034655925</v>
       </c>
       <c r="P76">
-        <v>4.449397554</v>
+        <v>4.410901575</v>
       </c>
       <c r="Q76">
-        <v>7.239397554000001</v>
+        <v>7.200901575</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.260734668458911</v>
+        <v>0.2688378605208946</v>
       </c>
       <c r="T76">
-        <v>3.936603934762732</v>
+        <v>4.085016743101471</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.561903230801663</v>
+        <v>2.527744521057641</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1108887151302237</v>
+        <v>0.1132903964611305</v>
       </c>
       <c r="C77">
-        <v>16.48421922049325</v>
+        <v>14.30858964049774</v>
       </c>
       <c r="D77">
-        <v>64.24921922049325</v>
+        <v>62.73458964049774</v>
       </c>
       <c r="E77">
-        <v>49.575</v>
+        <v>50.236</v>
       </c>
       <c r="F77">
-        <v>49.575</v>
+        <v>50.236</v>
       </c>
       <c r="G77">
         <v>1.81</v>
@@ -7601,45 +7601,45 @@
         <v>9.01</v>
       </c>
       <c r="M77">
-        <v>3.5644425</v>
+        <v>3.8078888</v>
       </c>
       <c r="N77">
-        <v>5.4455575</v>
+        <v>5.202111199999999</v>
       </c>
       <c r="O77">
-        <v>1.034655925</v>
+        <v>0.9884011279999999</v>
       </c>
       <c r="P77">
-        <v>4.410901575</v>
+        <v>4.213710072</v>
       </c>
       <c r="Q77">
-        <v>7.200901575</v>
+        <v>7.003710072000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2688378605208946</v>
+        <v>0.2776163185880435</v>
       </c>
       <c r="T77">
-        <v>4.085016743101471</v>
+        <v>4.24579728546844</v>
       </c>
       <c r="U77">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V77">
         <v>0.19</v>
       </c>
       <c r="W77">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.527744521057641</v>
+        <v>2.366140523851431</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1132903964611305</v>
+        <v>0.1133228277920372</v>
       </c>
       <c r="C78">
-        <v>14.30858964049774</v>
+        <v>13.62762521577897</v>
       </c>
       <c r="D78">
-        <v>62.73458964049774</v>
+        <v>62.71462521577897</v>
       </c>
       <c r="E78">
-        <v>50.236</v>
+        <v>50.897</v>
       </c>
       <c r="F78">
-        <v>50.236</v>
+        <v>50.897</v>
       </c>
       <c r="G78">
         <v>1.81</v>
@@ -7683,28 +7683,28 @@
         <v>9.01</v>
       </c>
       <c r="M78">
-        <v>3.8078888</v>
+        <v>3.8579926</v>
       </c>
       <c r="N78">
-        <v>5.202111199999999</v>
+        <v>5.1520074</v>
       </c>
       <c r="O78">
-        <v>0.9884011279999999</v>
+        <v>0.978881406</v>
       </c>
       <c r="P78">
-        <v>4.213710072</v>
+        <v>4.173125993999999</v>
       </c>
       <c r="Q78">
-        <v>7.003710072000001</v>
+        <v>6.963125994</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2776163185880435</v>
+        <v>0.2871581208349445</v>
       </c>
       <c r="T78">
-        <v>4.24579728546844</v>
+        <v>4.420558744562969</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.366140523851431</v>
+        <v>2.335411426139075</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1133228277920372</v>
+        <v>0.113355259122944</v>
       </c>
       <c r="C79">
-        <v>13.62762521577897</v>
+        <v>12.94667349382767</v>
       </c>
       <c r="D79">
-        <v>62.71462521577897</v>
+        <v>62.69467349382766</v>
       </c>
       <c r="E79">
-        <v>50.897</v>
+        <v>51.558</v>
       </c>
       <c r="F79">
-        <v>50.897</v>
+        <v>51.558</v>
       </c>
       <c r="G79">
         <v>1.81</v>
@@ -7765,28 +7765,28 @@
         <v>9.01</v>
       </c>
       <c r="M79">
-        <v>3.8579926</v>
+        <v>3.9080964</v>
       </c>
       <c r="N79">
-        <v>5.1520074</v>
+        <v>5.1019036</v>
       </c>
       <c r="O79">
-        <v>0.978881406</v>
+        <v>0.969361684</v>
       </c>
       <c r="P79">
-        <v>4.173125993999999</v>
+        <v>4.132541916</v>
       </c>
       <c r="Q79">
-        <v>6.963125994</v>
+        <v>6.922541916000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2871581208349445</v>
+        <v>0.2975673596497457</v>
       </c>
       <c r="T79">
-        <v>4.420558744562969</v>
+        <v>4.61120760902973</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.335411426139075</v>
+        <v>2.305470254009087</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.113355259122944</v>
+        <v>0.1133876904538508</v>
       </c>
       <c r="C80">
-        <v>12.94667349382767</v>
+        <v>12.26573446252412</v>
       </c>
       <c r="D80">
-        <v>62.69467349382766</v>
+        <v>62.67473446252411</v>
       </c>
       <c r="E80">
-        <v>51.558</v>
+        <v>52.219</v>
       </c>
       <c r="F80">
-        <v>51.558</v>
+        <v>52.219</v>
       </c>
       <c r="G80">
         <v>1.81</v>
@@ -7847,28 +7847,28 @@
         <v>9.01</v>
       </c>
       <c r="M80">
-        <v>3.9080964</v>
+        <v>3.9582002</v>
       </c>
       <c r="N80">
-        <v>5.1019036</v>
+        <v>5.0517998</v>
       </c>
       <c r="O80">
-        <v>0.969361684</v>
+        <v>0.9598419619999999</v>
       </c>
       <c r="P80">
-        <v>4.132541916</v>
+        <v>4.091957838</v>
       </c>
       <c r="Q80">
-        <v>6.922541916000001</v>
+        <v>6.881957838000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2975673596497457</v>
+        <v>0.3089679545421469</v>
       </c>
       <c r="T80">
-        <v>4.61120760902973</v>
+        <v>4.82001350820761</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.305470254009087</v>
+        <v>2.27628708623682</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1133876904538508</v>
+        <v>0.1134201217847576</v>
       </c>
       <c r="C81">
-        <v>12.26573446252412</v>
+        <v>11.58480810976401</v>
       </c>
       <c r="D81">
-        <v>62.67473446252411</v>
+        <v>62.65480810976401</v>
       </c>
       <c r="E81">
-        <v>52.219</v>
+        <v>52.88</v>
       </c>
       <c r="F81">
-        <v>52.219</v>
+        <v>52.88</v>
       </c>
       <c r="G81">
         <v>1.81</v>
@@ -7929,28 +7929,28 @@
         <v>9.01</v>
       </c>
       <c r="M81">
-        <v>3.9582002</v>
+        <v>4.008304</v>
       </c>
       <c r="N81">
-        <v>5.0517998</v>
+        <v>5.001696</v>
       </c>
       <c r="O81">
-        <v>0.9598419619999999</v>
+        <v>0.95032224</v>
       </c>
       <c r="P81">
-        <v>4.091957838</v>
+        <v>4.05137376</v>
       </c>
       <c r="Q81">
-        <v>6.881957838000001</v>
+        <v>6.841373760000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3089679545421469</v>
+        <v>0.3215086089237882</v>
       </c>
       <c r="T81">
-        <v>4.82001350820761</v>
+        <v>5.049699997303279</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.27628708623682</v>
+        <v>2.24783349765886</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1134201217847576</v>
+        <v>0.1134525531156644</v>
       </c>
       <c r="C82">
-        <v>11.58480810976401</v>
+        <v>10.9038944234584</v>
       </c>
       <c r="D82">
-        <v>62.65480810976401</v>
+        <v>62.6348944234584</v>
       </c>
       <c r="E82">
-        <v>52.88</v>
+        <v>53.541</v>
       </c>
       <c r="F82">
-        <v>52.88</v>
+        <v>53.541</v>
       </c>
       <c r="G82">
         <v>1.81</v>
@@ -8011,28 +8011,28 @@
         <v>9.01</v>
       </c>
       <c r="M82">
-        <v>4.008304</v>
+        <v>4.0584078</v>
       </c>
       <c r="N82">
-        <v>5.001696</v>
+        <v>4.951592199999999</v>
       </c>
       <c r="O82">
-        <v>0.95032224</v>
+        <v>0.9408025179999999</v>
       </c>
       <c r="P82">
-        <v>4.05137376</v>
+        <v>4.010789682</v>
       </c>
       <c r="Q82">
-        <v>6.841373760000001</v>
+        <v>6.800789682</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3215086089237882</v>
+        <v>0.3353693321877075</v>
       </c>
       <c r="T82">
-        <v>5.049699997303279</v>
+        <v>5.303564011566912</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.24783349765886</v>
+        <v>2.220082466823565</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1134525531156644</v>
+        <v>0.1134849844465712</v>
       </c>
       <c r="C83">
-        <v>10.9038944234584</v>
+        <v>10.22299339153372</v>
       </c>
       <c r="D83">
-        <v>62.6348944234584</v>
+        <v>62.61499339153372</v>
       </c>
       <c r="E83">
-        <v>53.541</v>
+        <v>54.202</v>
       </c>
       <c r="F83">
-        <v>53.541</v>
+        <v>54.202</v>
       </c>
       <c r="G83">
         <v>1.81</v>
@@ -8093,28 +8093,28 @@
         <v>9.01</v>
       </c>
       <c r="M83">
-        <v>4.0584078</v>
+        <v>4.1085116</v>
       </c>
       <c r="N83">
-        <v>4.951592199999999</v>
+        <v>4.9014884</v>
       </c>
       <c r="O83">
-        <v>0.9408025179999999</v>
+        <v>0.931282796</v>
       </c>
       <c r="P83">
-        <v>4.010789682</v>
+        <v>3.970205604</v>
       </c>
       <c r="Q83">
-        <v>6.800789682</v>
+        <v>6.760205604000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3353693321877075</v>
+        <v>0.3507701358142846</v>
       </c>
       <c r="T83">
-        <v>5.303564011566912</v>
+        <v>5.585635138526504</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.220082466823565</v>
+        <v>2.193008290398888</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1134849844465712</v>
+        <v>0.113517415777478</v>
       </c>
       <c r="C84">
-        <v>10.22299339153372</v>
+        <v>9.542105001931759</v>
       </c>
       <c r="D84">
-        <v>62.61499339153372</v>
+        <v>62.59510500193176</v>
       </c>
       <c r="E84">
-        <v>54.202</v>
+        <v>54.863</v>
       </c>
       <c r="F84">
-        <v>54.202</v>
+        <v>54.863</v>
       </c>
       <c r="G84">
         <v>1.81</v>
@@ -8175,28 +8175,28 @@
         <v>9.01</v>
       </c>
       <c r="M84">
-        <v>4.1085116</v>
+        <v>4.1586154</v>
       </c>
       <c r="N84">
-        <v>4.9014884</v>
+        <v>4.851384599999999</v>
       </c>
       <c r="O84">
-        <v>0.931282796</v>
+        <v>0.9217630739999999</v>
       </c>
       <c r="P84">
-        <v>3.970205604</v>
+        <v>3.929621526</v>
       </c>
       <c r="Q84">
-        <v>6.760205604000001</v>
+        <v>6.719621526000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3507701358142846</v>
+        <v>0.3679827986910472</v>
       </c>
       <c r="T84">
-        <v>5.585635138526504</v>
+        <v>5.900891103951931</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.193008290398888</v>
+        <v>2.166586503767576</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.113517415777478</v>
+        <v>0.1135498471083848</v>
       </c>
       <c r="C85">
-        <v>9.542105001931759</v>
+        <v>8.861229242609568</v>
       </c>
       <c r="D85">
-        <v>62.59510500193176</v>
+        <v>62.57522924260957</v>
       </c>
       <c r="E85">
-        <v>54.863</v>
+        <v>55.524</v>
       </c>
       <c r="F85">
-        <v>54.863</v>
+        <v>55.524</v>
       </c>
       <c r="G85">
         <v>1.81</v>
@@ -8257,28 +8257,28 @@
         <v>9.01</v>
       </c>
       <c r="M85">
-        <v>4.1586154</v>
+        <v>4.2087192</v>
       </c>
       <c r="N85">
-        <v>4.851384599999999</v>
+        <v>4.8012808</v>
       </c>
       <c r="O85">
-        <v>0.9217630739999999</v>
+        <v>0.912243352</v>
       </c>
       <c r="P85">
-        <v>3.929621526</v>
+        <v>3.889037448</v>
       </c>
       <c r="Q85">
-        <v>6.719621526000001</v>
+        <v>6.679037448000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3679827986910472</v>
+        <v>0.3873470444274051</v>
       </c>
       <c r="T85">
-        <v>5.900891103951931</v>
+        <v>6.255554065055537</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.166586503767576</v>
+        <v>2.140793807294153</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1135498471083848</v>
+        <v>0.1135822784392916</v>
       </c>
       <c r="C86">
-        <v>8.861229242609575</v>
+        <v>8.180366101539583</v>
       </c>
       <c r="D86">
-        <v>62.57522924260957</v>
+        <v>62.55536610153958</v>
       </c>
       <c r="E86">
-        <v>55.52399999999999</v>
+        <v>56.185</v>
       </c>
       <c r="F86">
-        <v>55.52399999999999</v>
+        <v>56.185</v>
       </c>
       <c r="G86">
         <v>1.81</v>
@@ -8339,28 +8339,28 @@
         <v>9.01</v>
       </c>
       <c r="M86">
-        <v>4.2087192</v>
+        <v>4.258823</v>
       </c>
       <c r="N86">
-        <v>4.8012808</v>
+        <v>4.751177</v>
       </c>
       <c r="O86">
-        <v>0.912243352</v>
+        <v>0.90272363</v>
       </c>
       <c r="P86">
-        <v>3.889037448</v>
+        <v>3.84845337</v>
       </c>
       <c r="Q86">
-        <v>6.679037448000001</v>
+        <v>6.638453370000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3873470444274049</v>
+        <v>0.4092931895952772</v>
       </c>
       <c r="T86">
-        <v>6.255554065055533</v>
+        <v>6.657505420972952</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.140793807294153</v>
+        <v>2.115607997796574</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1135822784392916</v>
+        <v>0.1136147097701984</v>
       </c>
       <c r="C87">
-        <v>8.180366101539583</v>
+        <v>7.499515566709412</v>
       </c>
       <c r="D87">
-        <v>62.55536610153958</v>
+        <v>62.53551556670941</v>
       </c>
       <c r="E87">
-        <v>56.185</v>
+        <v>56.846</v>
       </c>
       <c r="F87">
-        <v>56.185</v>
+        <v>56.846</v>
       </c>
       <c r="G87">
         <v>1.81</v>
@@ -8421,28 +8421,28 @@
         <v>9.01</v>
       </c>
       <c r="M87">
-        <v>4.258823</v>
+        <v>4.3089268</v>
       </c>
       <c r="N87">
-        <v>4.751177</v>
+        <v>4.7010732</v>
       </c>
       <c r="O87">
-        <v>0.90272363</v>
+        <v>0.8932039079999999</v>
       </c>
       <c r="P87">
-        <v>3.84845337</v>
+        <v>3.807869292</v>
       </c>
       <c r="Q87">
-        <v>6.638453370000001</v>
+        <v>6.597869292</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4092931895952772</v>
+        <v>0.4343744983585598</v>
       </c>
       <c r="T87">
-        <v>6.657505420972952</v>
+        <v>7.116878399164288</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.115607997796574</v>
+        <v>2.09100790479894</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1136147097701984</v>
+        <v>0.1136471411011052</v>
       </c>
       <c r="C88">
-        <v>7.499515566709412</v>
+        <v>6.818677626121932</v>
       </c>
       <c r="D88">
-        <v>62.53551556670941</v>
+        <v>62.51567762612193</v>
       </c>
       <c r="E88">
-        <v>56.846</v>
+        <v>57.507</v>
       </c>
       <c r="F88">
-        <v>56.846</v>
+        <v>57.507</v>
       </c>
       <c r="G88">
         <v>1.81</v>
@@ -8503,28 +8503,28 @@
         <v>9.01</v>
       </c>
       <c r="M88">
-        <v>4.3089268</v>
+        <v>4.359030600000001</v>
       </c>
       <c r="N88">
-        <v>4.7010732</v>
+        <v>4.650969399999999</v>
       </c>
       <c r="O88">
-        <v>0.8932039079999999</v>
+        <v>0.8836841859999999</v>
       </c>
       <c r="P88">
-        <v>3.807869292</v>
+        <v>3.767285213999999</v>
       </c>
       <c r="Q88">
-        <v>6.597869292</v>
+        <v>6.557285214</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4343744983585598</v>
+        <v>0.4633144700085013</v>
       </c>
       <c r="T88">
-        <v>7.116878399164288</v>
+        <v>7.646924143231214</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.09100790479894</v>
+        <v>2.066973331180561</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1136471411011052</v>
+        <v>0.113679572432012</v>
       </c>
       <c r="C89">
-        <v>6.818677626121932</v>
+        <v>6.137852267795296</v>
       </c>
       <c r="D89">
-        <v>62.51567762612193</v>
+        <v>62.49585226779529</v>
       </c>
       <c r="E89">
-        <v>57.507</v>
+        <v>58.16799999999999</v>
       </c>
       <c r="F89">
-        <v>57.507</v>
+        <v>58.16799999999999</v>
       </c>
       <c r="G89">
         <v>1.81</v>
@@ -8585,28 +8585,28 @@
         <v>9.01</v>
       </c>
       <c r="M89">
-        <v>4.359030600000001</v>
+        <v>4.4091344</v>
       </c>
       <c r="N89">
-        <v>4.650969399999999</v>
+        <v>4.6008656</v>
       </c>
       <c r="O89">
-        <v>0.8836841859999999</v>
+        <v>0.8741644639999999</v>
       </c>
       <c r="P89">
-        <v>3.767285213999999</v>
+        <v>3.726701136</v>
       </c>
       <c r="Q89">
-        <v>6.557285214</v>
+        <v>6.516701136000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4633144700085013</v>
+        <v>0.4970777702667665</v>
       </c>
       <c r="T89">
-        <v>7.646924143231214</v>
+        <v>8.265310844642629</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.066973331180561</v>
+        <v>2.043484997871691</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.113679572432012</v>
+        <v>0.1137120037629188</v>
       </c>
       <c r="C90">
-        <v>6.137852267795296</v>
+        <v>5.457039479762784</v>
       </c>
       <c r="D90">
-        <v>62.49585226779529</v>
+        <v>62.47603947976278</v>
       </c>
       <c r="E90">
-        <v>58.16799999999999</v>
+        <v>58.82899999999999</v>
       </c>
       <c r="F90">
-        <v>58.16799999999999</v>
+        <v>58.82899999999999</v>
       </c>
       <c r="G90">
         <v>1.81</v>
@@ -8667,28 +8667,28 @@
         <v>9.01</v>
       </c>
       <c r="M90">
-        <v>4.4091344</v>
+        <v>4.4592382</v>
       </c>
       <c r="N90">
-        <v>4.6008656</v>
+        <v>4.5507618</v>
       </c>
       <c r="O90">
-        <v>0.8741644639999999</v>
+        <v>0.8646447420000001</v>
       </c>
       <c r="P90">
-        <v>3.726701136</v>
+        <v>3.686117058</v>
       </c>
       <c r="Q90">
-        <v>6.516701136000001</v>
+        <v>6.476117058000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4970777702667665</v>
+        <v>0.5369798523901705</v>
       </c>
       <c r="T90">
-        <v>8.265310844642629</v>
+        <v>8.996131491765208</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.043484997871691</v>
+        <v>2.020524492277628</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1137120037629188</v>
+        <v>0.1240962350938256</v>
       </c>
       <c r="C91">
-        <v>5.457039479762784</v>
+        <v>-0.961401229774431</v>
       </c>
       <c r="D91">
-        <v>62.47603947976278</v>
+        <v>56.71859877022556</v>
       </c>
       <c r="E91">
-        <v>58.82899999999999</v>
+        <v>59.48999999999999</v>
       </c>
       <c r="F91">
-        <v>58.82899999999999</v>
+        <v>59.48999999999999</v>
       </c>
       <c r="G91">
         <v>1.81</v>
@@ -8749,45 +8749,45 @@
         <v>9.01</v>
       </c>
       <c r="M91">
-        <v>4.4592382</v>
+        <v>5.354099999999999</v>
       </c>
       <c r="N91">
-        <v>4.5507618</v>
+        <v>3.655900000000001</v>
       </c>
       <c r="O91">
-        <v>0.8646447420000001</v>
+        <v>0.6946210000000002</v>
       </c>
       <c r="P91">
-        <v>3.686117058</v>
+        <v>2.961279000000001</v>
       </c>
       <c r="Q91">
-        <v>6.476117058000001</v>
+        <v>5.751279000000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5369798523901705</v>
+        <v>0.5848623509382557</v>
       </c>
       <c r="T91">
-        <v>8.996131491765208</v>
+        <v>9.873116268312307</v>
       </c>
       <c r="U91">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V91">
         <v>0.19</v>
       </c>
       <c r="W91">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.020524492277628</v>
+        <v>1.682822509852263</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1240962350938256</v>
+        <v>0.1242436864247324</v>
       </c>
       <c r="C92">
-        <v>-0.961401229774431</v>
+        <v>-1.696523360413195</v>
       </c>
       <c r="D92">
-        <v>56.71859877022556</v>
+        <v>56.6444766395868</v>
       </c>
       <c r="E92">
-        <v>59.48999999999999</v>
+        <v>60.151</v>
       </c>
       <c r="F92">
-        <v>59.48999999999999</v>
+        <v>60.151</v>
       </c>
       <c r="G92">
         <v>1.81</v>
@@ -8831,28 +8831,28 @@
         <v>9.01</v>
       </c>
       <c r="M92">
-        <v>5.354099999999999</v>
+        <v>5.413589999999999</v>
       </c>
       <c r="N92">
-        <v>3.655900000000001</v>
+        <v>3.596410000000001</v>
       </c>
       <c r="O92">
-        <v>0.6946210000000002</v>
+        <v>0.6833179000000001</v>
       </c>
       <c r="P92">
-        <v>2.961279000000001</v>
+        <v>2.913092100000001</v>
       </c>
       <c r="Q92">
-        <v>5.751279000000002</v>
+        <v>5.703092100000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5848623509382557</v>
+        <v>0.6433854047192484</v>
       </c>
       <c r="T92">
-        <v>9.873116268312307</v>
+        <v>10.94498655075876</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.682822509852263</v>
+        <v>1.664329954798941</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1242436864247324</v>
+        <v>0.1243911377556391</v>
       </c>
       <c r="C93">
-        <v>-1.696523360413195</v>
+        <v>-2.43145201237499</v>
       </c>
       <c r="D93">
-        <v>56.6444766395868</v>
+        <v>56.57054798762501</v>
       </c>
       <c r="E93">
-        <v>60.151</v>
+        <v>60.812</v>
       </c>
       <c r="F93">
-        <v>60.151</v>
+        <v>60.812</v>
       </c>
       <c r="G93">
         <v>1.81</v>
@@ -8913,28 +8913,28 @@
         <v>9.01</v>
       </c>
       <c r="M93">
-        <v>5.413589999999999</v>
+        <v>5.47308</v>
       </c>
       <c r="N93">
-        <v>3.596410000000001</v>
+        <v>3.53692</v>
       </c>
       <c r="O93">
-        <v>0.6833179000000001</v>
+        <v>0.6720148</v>
       </c>
       <c r="P93">
-        <v>2.913092100000001</v>
+        <v>2.8649052</v>
       </c>
       <c r="Q93">
-        <v>5.703092100000001</v>
+        <v>5.654905200000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6433854047192484</v>
+        <v>0.7165392219454896</v>
       </c>
       <c r="T93">
-        <v>10.94498655075876</v>
+        <v>12.28482440381682</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.664329954798941</v>
+        <v>1.646239411811996</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1243911377556391</v>
+        <v>0.1245385890865459</v>
       </c>
       <c r="C94">
-        <v>-2.43145201237499</v>
+        <v>-3.166187942219402</v>
       </c>
       <c r="D94">
-        <v>56.57054798762501</v>
+        <v>56.49681205778059</v>
       </c>
       <c r="E94">
-        <v>60.812</v>
+        <v>61.473</v>
       </c>
       <c r="F94">
-        <v>60.812</v>
+        <v>61.473</v>
       </c>
       <c r="G94">
         <v>1.81</v>
@@ -8995,28 +8995,28 @@
         <v>9.01</v>
       </c>
       <c r="M94">
-        <v>5.47308</v>
+        <v>5.53257</v>
       </c>
       <c r="N94">
-        <v>3.53692</v>
+        <v>3.47743</v>
       </c>
       <c r="O94">
-        <v>0.6720148</v>
+        <v>0.6607117</v>
       </c>
       <c r="P94">
-        <v>2.8649052</v>
+        <v>2.8167183</v>
       </c>
       <c r="Q94">
-        <v>5.654905200000002</v>
+        <v>5.606718300000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7165392219454896</v>
+        <v>0.8105941298077994</v>
       </c>
       <c r="T94">
-        <v>12.28482440381682</v>
+        <v>14.00747307203434</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.646239411811996</v>
+        <v>1.628537912760254</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1245385890865459</v>
+        <v>0.1246860404174527</v>
       </c>
       <c r="C95">
-        <v>-3.166187942219402</v>
+        <v>-3.900731902566676</v>
       </c>
       <c r="D95">
-        <v>56.49681205778059</v>
+        <v>56.42326809743332</v>
       </c>
       <c r="E95">
-        <v>61.473</v>
+        <v>62.134</v>
       </c>
       <c r="F95">
-        <v>61.473</v>
+        <v>62.134</v>
       </c>
       <c r="G95">
         <v>1.81</v>
@@ -9077,28 +9077,28 @@
         <v>9.01</v>
       </c>
       <c r="M95">
-        <v>5.53257</v>
+        <v>5.59206</v>
       </c>
       <c r="N95">
-        <v>3.47743</v>
+        <v>3.41794</v>
       </c>
       <c r="O95">
-        <v>0.6607117</v>
+        <v>0.6494086</v>
       </c>
       <c r="P95">
-        <v>2.8167183</v>
+        <v>2.7685314</v>
       </c>
       <c r="Q95">
-        <v>5.606718300000001</v>
+        <v>5.558531400000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8105941298077994</v>
+        <v>0.9360006736242129</v>
       </c>
       <c r="T95">
-        <v>14.00747307203434</v>
+        <v>16.30433796299102</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.628537912760254</v>
+        <v>1.611213041347911</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1246860404174527</v>
+        <v>0.1248334917483595</v>
       </c>
       <c r="C96">
-        <v>-3.900731902566676</v>
+        <v>-4.635084642123275</v>
       </c>
       <c r="D96">
-        <v>56.42326809743332</v>
+        <v>56.34991535787672</v>
       </c>
       <c r="E96">
-        <v>62.134</v>
+        <v>62.795</v>
       </c>
       <c r="F96">
-        <v>62.134</v>
+        <v>62.795</v>
       </c>
       <c r="G96">
         <v>1.81</v>
@@ -9159,28 +9159,28 @@
         <v>9.01</v>
       </c>
       <c r="M96">
-        <v>5.59206</v>
+        <v>5.65155</v>
       </c>
       <c r="N96">
-        <v>3.41794</v>
+        <v>3.358449999999999</v>
       </c>
       <c r="O96">
-        <v>0.6494086</v>
+        <v>0.6381054999999999</v>
       </c>
       <c r="P96">
-        <v>2.7685314</v>
+        <v>2.720344499999999</v>
       </c>
       <c r="Q96">
-        <v>5.558531400000001</v>
+        <v>5.5103445</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9360006736242129</v>
+        <v>1.111569834967192</v>
       </c>
       <c r="T96">
-        <v>16.30433796299102</v>
+        <v>19.51994881033038</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.611213041347911</v>
+        <v>1.594252904070565</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1248334917483595</v>
+        <v>0.1249809430792663</v>
       </c>
       <c r="C97">
-        <v>-4.635084642123275</v>
+        <v>-5.3692469057073</v>
       </c>
       <c r="D97">
-        <v>56.34991535787672</v>
+        <v>56.2767530942927</v>
       </c>
       <c r="E97">
-        <v>62.795</v>
+        <v>63.456</v>
       </c>
       <c r="F97">
-        <v>62.795</v>
+        <v>63.456</v>
       </c>
       <c r="G97">
         <v>1.81</v>
@@ -9241,28 +9241,28 @@
         <v>9.01</v>
       </c>
       <c r="M97">
-        <v>5.65155</v>
+        <v>5.71104</v>
       </c>
       <c r="N97">
-        <v>3.358449999999999</v>
+        <v>3.29896</v>
       </c>
       <c r="O97">
-        <v>0.6381054999999999</v>
+        <v>0.6268024</v>
       </c>
       <c r="P97">
-        <v>2.720344499999999</v>
+        <v>2.6721576</v>
       </c>
       <c r="Q97">
-        <v>5.5103445</v>
+        <v>5.462157600000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.111569834967192</v>
+        <v>1.374923576981661</v>
       </c>
       <c r="T97">
-        <v>19.51994881033038</v>
+        <v>24.34336508133943</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.594252904070565</v>
+        <v>1.577646102986496</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1249809430792663</v>
+        <v>0.1251283944101731</v>
       </c>
       <c r="C98">
-        <v>-5.369246905707278</v>
+        <v>-6.103219434273704</v>
       </c>
       <c r="D98">
-        <v>56.27675309429271</v>
+        <v>56.20378056572628</v>
       </c>
       <c r="E98">
-        <v>63.45599999999999</v>
+        <v>64.11699999999999</v>
       </c>
       <c r="F98">
-        <v>63.45599999999999</v>
+        <v>64.11699999999999</v>
       </c>
       <c r="G98">
         <v>1.81</v>
@@ -9323,28 +9323,28 @@
         <v>9.01</v>
       </c>
       <c r="M98">
-        <v>5.711039999999999</v>
+        <v>5.770529999999999</v>
       </c>
       <c r="N98">
-        <v>3.298960000000001</v>
+        <v>3.239470000000001</v>
       </c>
       <c r="O98">
-        <v>0.6268024000000002</v>
+        <v>0.6154993000000002</v>
       </c>
       <c r="P98">
-        <v>2.672157600000001</v>
+        <v>2.623970700000001</v>
       </c>
       <c r="Q98">
-        <v>5.462157600000001</v>
+        <v>5.413970700000002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.374923576981657</v>
+        <v>1.813846480339102</v>
       </c>
       <c r="T98">
-        <v>24.34336508133936</v>
+        <v>32.38239219968774</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.577646102986497</v>
+        <v>1.561381710172203</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1251283944101731</v>
+        <v>0.1252758457410799</v>
       </c>
       <c r="C99">
-        <v>-6.103219434273704</v>
+        <v>-6.837002964939366</v>
       </c>
       <c r="D99">
-        <v>56.20378056572628</v>
+        <v>56.13099703506062</v>
       </c>
       <c r="E99">
-        <v>64.11699999999999</v>
+        <v>64.77799999999999</v>
       </c>
       <c r="F99">
-        <v>64.11699999999999</v>
+        <v>64.77799999999999</v>
       </c>
       <c r="G99">
         <v>1.81</v>
@@ -9405,28 +9405,28 @@
         <v>9.01</v>
       </c>
       <c r="M99">
-        <v>5.770529999999999</v>
+        <v>5.830019999999999</v>
       </c>
       <c r="N99">
-        <v>3.239470000000001</v>
+        <v>3.17998</v>
       </c>
       <c r="O99">
-        <v>0.6154993000000002</v>
+        <v>0.6041962000000001</v>
       </c>
       <c r="P99">
-        <v>2.623970700000001</v>
+        <v>2.5757838</v>
       </c>
       <c r="Q99">
-        <v>5.413970700000002</v>
+        <v>5.365783800000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.813846480339102</v>
+        <v>2.691692287053993</v>
       </c>
       <c r="T99">
-        <v>32.38239219968774</v>
+        <v>48.46044643638448</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.561381710172203</v>
+        <v>1.545449243741874</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1252758457410799</v>
+        <v>0.1254232970719867</v>
       </c>
       <c r="C100">
-        <v>-6.837002964939366</v>
+        <v>-7.5705982310078</v>
       </c>
       <c r="D100">
-        <v>56.13099703506062</v>
+        <v>56.05840176899219</v>
       </c>
       <c r="E100">
-        <v>64.77799999999999</v>
+        <v>65.43899999999999</v>
       </c>
       <c r="F100">
-        <v>64.77799999999999</v>
+        <v>65.43899999999999</v>
       </c>
       <c r="G100">
         <v>1.81</v>
@@ -9487,28 +9487,28 @@
         <v>9.01</v>
       </c>
       <c r="M100">
-        <v>5.830019999999999</v>
+        <v>5.88951</v>
       </c>
       <c r="N100">
-        <v>3.17998</v>
+        <v>3.12049</v>
       </c>
       <c r="O100">
-        <v>0.6041962000000001</v>
+        <v>0.5928931000000001</v>
       </c>
       <c r="P100">
-        <v>2.5757838</v>
+        <v>2.5275969</v>
       </c>
       <c r="Q100">
-        <v>5.365783800000001</v>
+        <v>5.317596900000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.691692287053993</v>
+        <v>5.325229707198665</v>
       </c>
       <c r="T100">
-        <v>48.46044643638448</v>
+        <v>96.6946091464747</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.545449243741874</v>
+        <v>1.529838645320239</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1254232970719867</v>
-      </c>
-      <c r="C101">
-        <v>-7.5705982310078</v>
-      </c>
-      <c r="D101">
-        <v>56.05840176899219</v>
-      </c>
-      <c r="E101">
-        <v>65.43899999999999</v>
-      </c>
-      <c r="F101">
-        <v>65.43899999999999</v>
-      </c>
-      <c r="G101">
-        <v>1.81</v>
-      </c>
-      <c r="H101">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.8</v>
-      </c>
-      <c r="K101">
-        <v>2.790000000000001</v>
-      </c>
-      <c r="L101">
-        <v>9.01</v>
-      </c>
-      <c r="M101">
-        <v>5.88951</v>
-      </c>
-      <c r="N101">
-        <v>3.12049</v>
-      </c>
-      <c r="O101">
-        <v>0.5928931000000001</v>
-      </c>
-      <c r="P101">
-        <v>2.5275969</v>
-      </c>
-      <c r="Q101">
-        <v>5.317596900000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.325229707198665</v>
-      </c>
-      <c r="T101">
-        <v>96.6946091464747</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.19</v>
-      </c>
-      <c r="W101">
-        <v>0.07290000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.529838645320239</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
